--- a/New_Outputs/multivariable_regression/Stats_MVR_ROE_Receptor_NRS.xlsx
+++ b/New_Outputs/multivariable_regression/Stats_MVR_ROE_Receptor_NRS.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="55">
   <si>
     <t>group</t>
   </si>
@@ -656,10 +656,10 @@
         <v>0.001924135753232891</v>
       </c>
       <c r="T2">
-        <v>0.03939794677721668</v>
+        <v>0.00401557133453159</v>
       </c>
       <c r="U2">
-        <v>0.05953933996031915</v>
+        <v>0.02899989459508442</v>
       </c>
       <c r="V2" t="b">
         <v>1</v>
@@ -727,10 +727,10 @@
         <v>0.001982944495211959</v>
       </c>
       <c r="T3">
-        <v>0.03939794677721668</v>
+        <v>0.004147152292338598</v>
       </c>
       <c r="U3">
-        <v>0.05953933996031915</v>
+        <v>0.005793488543173329</v>
       </c>
       <c r="V3" t="b">
         <v>1</v>
@@ -798,16 +798,16 @@
         <v>0.004030459392074336</v>
       </c>
       <c r="T4">
-        <v>0.0564639175648963</v>
+        <v>0.008915355404983626</v>
       </c>
       <c r="U4">
-        <v>0.05953933996031915</v>
+        <v>0.01106990333221139</v>
       </c>
       <c r="V4" t="b">
         <v>1</v>
       </c>
       <c r="W4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:23">
@@ -869,16 +869,16 @@
         <v>0.01592689317284809</v>
       </c>
       <c r="T5">
-        <v>0.1682632520385084</v>
+        <v>0.04112387770356465</v>
       </c>
       <c r="U5">
-        <v>0.05953933996031915</v>
+        <v>0.02428101019834354</v>
       </c>
       <c r="V5" t="b">
         <v>1</v>
       </c>
       <c r="W5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:23">
@@ -940,16 +940,16 @@
         <v>0.01698656083215125</v>
       </c>
       <c r="T6">
-        <v>0.1682632520385084</v>
+        <v>0.04427980316802854</v>
       </c>
       <c r="U6">
-        <v>0.05953933996031915</v>
+        <v>0.02704165709062151</v>
       </c>
       <c r="V6" t="b">
         <v>1</v>
       </c>
       <c r="W6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:23">
@@ -1011,10 +1011,10 @@
         <v>0.02359149260414747</v>
       </c>
       <c r="T7">
-        <v>0.2054176203622925</v>
+        <v>0.06486872221967133</v>
       </c>
       <c r="U7">
-        <v>0.05953933996031915</v>
+        <v>0.04366733272239159</v>
       </c>
       <c r="V7" t="b">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0.03731723881839773</v>
       </c>
       <c r="T8">
-        <v>0.3054115985246679</v>
+        <v>0.1125200626143513</v>
       </c>
       <c r="U8">
-        <v>0.05953933996031915</v>
+        <v>0.04692806961885894</v>
       </c>
       <c r="V8" t="b">
         <v>0</v>
@@ -1153,10 +1153,10 @@
         <v>0.04542392877196608</v>
       </c>
       <c r="T9">
-        <v>0.3356026753555522</v>
+        <v>0.1437753082918942</v>
       </c>
       <c r="U9">
-        <v>0.06508229807787605</v>
+        <v>0.06165691396851415</v>
       </c>
       <c r="V9" t="b">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0.04915365526352789</v>
       </c>
       <c r="T10">
-        <v>0.3356026753555522</v>
+        <v>0.1589696883263142</v>
       </c>
       <c r="U10">
-        <v>0.05953933996031915</v>
+        <v>0.03160548983618443</v>
       </c>
       <c r="V10" t="b">
         <v>0</v>
@@ -1295,10 +1295,10 @@
         <v>0.06537551205920639</v>
       </c>
       <c r="T11">
-        <v>0.3932299610771405</v>
+        <v>0.2316309263080703</v>
       </c>
       <c r="U11">
-        <v>0.05953933996031915</v>
+        <v>0.03087957842271282</v>
       </c>
       <c r="V11" t="b">
         <v>0</v>
@@ -1366,10 +1366,10 @@
         <v>0.06774441976825889</v>
       </c>
       <c r="T12">
-        <v>0.3932299610771405</v>
+        <v>0.2432283212671866</v>
       </c>
       <c r="U12">
-        <v>0.05953933996031915</v>
+        <v>0.0338921169339256</v>
       </c>
       <c r="V12" t="b">
         <v>0</v>
@@ -1437,10 +1437,10 @@
         <v>0.06877409322085867</v>
       </c>
       <c r="T13">
-        <v>0.3932299610771405</v>
+        <v>0.2483557648908256</v>
       </c>
       <c r="U13">
-        <v>0.05953933996031915</v>
+        <v>0.02895526728386478</v>
       </c>
       <c r="V13" t="b">
         <v>0</v>
@@ -1508,10 +1508,10 @@
         <v>0.07442394836772885</v>
       </c>
       <c r="T14">
-        <v>0.4055401192665947</v>
+        <v>0.2774748184455648</v>
       </c>
       <c r="U14">
-        <v>0.05953933996031915</v>
+        <v>0.02702920595243895</v>
       </c>
       <c r="V14" t="b">
         <v>0</v>
@@ -1579,7 +1579,7 @@
         <v>0.07859654973329193</v>
       </c>
       <c r="T15">
-        <v>0.4073152161111558</v>
+        <v>0.3001270013450621</v>
       </c>
       <c r="U15">
         <v>0.06867714314795682</v>
@@ -1650,10 +1650,10 @@
         <v>0.09418904924723714</v>
       </c>
       <c r="T16">
-        <v>0.5006632604860186</v>
+        <v>0.3952604688047515</v>
       </c>
       <c r="U16">
-        <v>0.05953933996031915</v>
+        <v>0.04700474207393617</v>
       </c>
       <c r="V16" t="b">
         <v>0</v>
@@ -1721,10 +1721,10 @@
         <v>0.1058276068550141</v>
       </c>
       <c r="T17">
-        <v>0.5710803399046239</v>
+        <v>0.4809097599196833</v>
       </c>
       <c r="U17">
-        <v>0.06057424596169279</v>
+        <v>0.05419800954467249</v>
       </c>
       <c r="V17" t="b">
         <v>0</v>
@@ -1792,10 +1792,10 @@
         <v>0.1203168776218692</v>
       </c>
       <c r="T18">
-        <v>0.6498613252573568</v>
+        <v>0.618470367699212</v>
       </c>
       <c r="U18">
-        <v>0.05953933996031915</v>
+        <v>0.04560325889351385</v>
       </c>
       <c r="V18" t="b">
         <v>0</v>
@@ -1863,10 +1863,10 @@
         <v>0.1204849591379604</v>
       </c>
       <c r="T19">
-        <v>0.6498613252573568</v>
+        <v>0.6203920622497769</v>
       </c>
       <c r="U19">
-        <v>0.05953933996031915</v>
+        <v>0.04279187982902813</v>
       </c>
       <c r="V19" t="b">
         <v>0</v>
@@ -1937,7 +1937,7 @@
         <v>0.6498613252573568</v>
       </c>
       <c r="U20">
-        <v>0.06012962265566948</v>
+        <v>0.05063547171003746</v>
       </c>
       <c r="V20" t="b">
         <v>0</v>
@@ -2005,16 +2005,16 @@
         <v>0.002253486890922358</v>
       </c>
       <c r="T21">
-        <v>0.06466302238962984</v>
+        <v>0.003403316967875255</v>
       </c>
       <c r="U21">
-        <v>0.08708871779725239</v>
+        <v>0.004583616726171178</v>
       </c>
       <c r="V21" t="b">
         <v>1</v>
       </c>
       <c r="W21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:23">
@@ -2076,10 +2076,10 @@
         <v>0.02787793517381637</v>
       </c>
       <c r="T22">
-        <v>0.4411025270837003</v>
+        <v>0.05409631121523648</v>
       </c>
       <c r="U22">
-        <v>0.08722502937508089</v>
+        <v>0.03506768618544823</v>
       </c>
       <c r="V22" t="b">
         <v>0</v>
@@ -2147,10 +2147,10 @@
         <v>0.03461555635132625</v>
       </c>
       <c r="T23">
-        <v>0.4411025270837003</v>
+        <v>0.06964776743426847</v>
       </c>
       <c r="U23">
-        <v>0.08722502937508089</v>
+        <v>0.04119307215965985</v>
       </c>
       <c r="V23" t="b">
         <v>0</v>
@@ -2218,10 +2218,10 @@
         <v>0.05560988889505961</v>
       </c>
       <c r="T24">
-        <v>0.5855432231957938</v>
+        <v>0.123272257514904</v>
       </c>
       <c r="U24">
-        <v>0.08722502937508089</v>
+        <v>0.04600223822670657</v>
       </c>
       <c r="V24" t="b">
         <v>0</v>
@@ -2289,10 +2289,10 @@
         <v>0.0714024549998958</v>
       </c>
       <c r="T25">
-        <v>0.6419567155485885</v>
+        <v>0.1689359777759444</v>
       </c>
       <c r="U25">
-        <v>0.08722502937508089</v>
+        <v>0.04476199304758969</v>
       </c>
       <c r="V25" t="b">
         <v>0</v>
@@ -2360,10 +2360,10 @@
         <v>0.1239623196254363</v>
       </c>
       <c r="T26">
-        <v>0.95969544087954</v>
+        <v>0.3631163930112545</v>
       </c>
       <c r="U26">
-        <v>0.08722502937508089</v>
+        <v>0.04716892439075019</v>
       </c>
       <c r="V26" t="b">
         <v>0</v>
@@ -2431,7 +2431,7 @@
         <v>0.1334874709482317</v>
       </c>
       <c r="T27">
-        <v>0.95969544087954</v>
+        <v>0.4081553476384943</v>
       </c>
       <c r="U27">
         <v>0.1217724614288306</v>
@@ -2502,10 +2502,10 @@
         <v>0.1499531925851488</v>
       </c>
       <c r="T28">
-        <v>0.95969544087954</v>
+        <v>0.497795655580913</v>
       </c>
       <c r="U28">
-        <v>0.08722502937508089</v>
+        <v>0.0563890368503555</v>
       </c>
       <c r="V28" t="b">
         <v>0</v>
@@ -2573,10 +2573,10 @@
         <v>0.1558825571892798</v>
       </c>
       <c r="T29">
-        <v>0.95969544087954</v>
+        <v>0.5350572518374678</v>
       </c>
       <c r="U29">
-        <v>0.08722502937508089</v>
+        <v>0.07125278390412024</v>
       </c>
       <c r="V29" t="b">
         <v>0</v>
@@ -2644,10 +2644,10 @@
         <v>0.1606109475205406</v>
       </c>
       <c r="T30">
-        <v>0.95969544087954</v>
+        <v>0.5673721116593613</v>
       </c>
       <c r="U30">
-        <v>0.08722502937508089</v>
+        <v>0.06675309637726333</v>
       </c>
       <c r="V30" t="b">
         <v>0</v>
@@ -2715,10 +2715,10 @@
         <v>0.164385691920056</v>
       </c>
       <c r="T31">
-        <v>0.95969544087954</v>
+        <v>0.5952231920428072</v>
       </c>
       <c r="U31">
-        <v>0.08722502937508089</v>
+        <v>0.06212650874073982</v>
       </c>
       <c r="V31" t="b">
         <v>0</v>
@@ -2786,10 +2786,10 @@
         <v>0.1668844505736522</v>
       </c>
       <c r="T32">
-        <v>0.95969544087954</v>
+        <v>0.6148709436016768</v>
       </c>
       <c r="U32">
-        <v>0.08722502937508089</v>
+        <v>0.06479240799018404</v>
       </c>
       <c r="V32" t="b">
         <v>0</v>
@@ -2857,10 +2857,10 @@
         <v>0.1775610419942558</v>
       </c>
       <c r="T33">
-        <v>0.95969544087954</v>
+        <v>0.7148771940079472</v>
       </c>
       <c r="U33">
-        <v>0.08722502937508089</v>
+        <v>0.06816174184725048</v>
       </c>
       <c r="V33" t="b">
         <v>0</v>
@@ -2928,10 +2928,10 @@
         <v>0.1830816576793275</v>
       </c>
       <c r="T34">
-        <v>0.95969544087954</v>
+        <v>0.785088009960876</v>
       </c>
       <c r="U34">
-        <v>0.08722502937508089</v>
+        <v>0.07138513624976332</v>
       </c>
       <c r="V34" t="b">
         <v>0</v>
@@ -2999,10 +2999,10 @@
         <v>0.1840517612361708</v>
       </c>
       <c r="T35">
-        <v>0.95969544087954</v>
+        <v>0.8000331750239781</v>
       </c>
       <c r="U35">
-        <v>0.08722502937508089</v>
+        <v>0.07126992481601897</v>
       </c>
       <c r="V35" t="b">
         <v>0</v>
@@ -3070,10 +3070,10 @@
         <v>0.1862503538953123</v>
       </c>
       <c r="T36">
-        <v>0.95969544087954</v>
+        <v>0.8390647212927266</v>
       </c>
       <c r="U36">
-        <v>0.08722502937508089</v>
+        <v>0.07169979159724997</v>
       </c>
       <c r="V36" t="b">
         <v>0</v>
@@ -3141,10 +3141,10 @@
         <v>0.1880388757873771</v>
       </c>
       <c r="T37">
-        <v>0.95969544087954</v>
+        <v>0.8799747781213381</v>
       </c>
       <c r="U37">
-        <v>0.1060812520440861</v>
+        <v>0.1004980282522921</v>
       </c>
       <c r="V37" t="b">
         <v>0</v>
@@ -3212,10 +3212,10 @@
         <v>0.1889952013385032</v>
       </c>
       <c r="T38">
-        <v>0.95969544087954</v>
+        <v>0.9091851545174588</v>
       </c>
       <c r="U38">
-        <v>0.1060812520440861</v>
+        <v>0.09639161779727942</v>
       </c>
       <c r="V38" t="b">
         <v>0</v>
@@ -3286,7 +3286,7 @@
         <v>0.9943910407898504</v>
       </c>
       <c r="U39">
-        <v>0.08722502937508089</v>
+        <v>0.0734526563158576</v>
       </c>
       <c r="V39" t="b">
         <v>0</v>
@@ -3363,10 +3363,10 @@
         <v>0.9091851545174588</v>
       </c>
       <c r="H2">
-        <v>0.0564639175648963</v>
+        <v>0.008915355404983626</v>
       </c>
       <c r="I2">
-        <v>0.95969544087954</v>
+        <v>0.9091851545174588</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
@@ -3398,7 +3398,7 @@
         <v>0.9943910407898504</v>
       </c>
       <c r="H3">
-        <v>0.1682632520385084</v>
+        <v>0.04112387770356465</v>
       </c>
       <c r="I3">
         <v>0.9943910407898504</v>
@@ -3433,10 +3433,10 @@
         <v>0.6148709436016768</v>
       </c>
       <c r="H4">
-        <v>0.03939794677721668</v>
+        <v>0.00401557133453159</v>
       </c>
       <c r="I4">
-        <v>0.95969544087954</v>
+        <v>0.6148709436016768</v>
       </c>
       <c r="J4" t="b">
         <v>0</v>
@@ -3468,10 +3468,10 @@
         <v>0.785088009960876</v>
       </c>
       <c r="H5">
-        <v>0.03939794677721668</v>
+        <v>0.004147152292338598</v>
       </c>
       <c r="I5">
-        <v>0.95969544087954</v>
+        <v>0.785088009960876</v>
       </c>
       <c r="J5" t="b">
         <v>0</v>
@@ -3503,10 +3503,10 @@
         <v>0.06964776743426847</v>
       </c>
       <c r="H6">
-        <v>0.1682632520385084</v>
+        <v>0.04427980316802854</v>
       </c>
       <c r="I6">
-        <v>0.4411025270837003</v>
+        <v>0.06964776743426847</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
@@ -3538,10 +3538,10 @@
         <v>0.123272257514904</v>
       </c>
       <c r="H7">
-        <v>0.2054176203622925</v>
+        <v>0.06486872221967133</v>
       </c>
       <c r="I7">
-        <v>0.5855432231957938</v>
+        <v>0.123272257514904</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
@@ -3573,10 +3573,10 @@
         <v>0.8000331750239781</v>
       </c>
       <c r="H8">
-        <v>0.3054115985246679</v>
+        <v>0.1125200626143513</v>
       </c>
       <c r="I8">
-        <v>0.95969544087954</v>
+        <v>0.8000331750239781</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
@@ -3608,10 +3608,10 @@
         <v>0.3631163930112545</v>
       </c>
       <c r="H9">
-        <v>0.3356026753555522</v>
+        <v>0.1437753082918942</v>
       </c>
       <c r="I9">
-        <v>0.95969544087954</v>
+        <v>0.3631163930112545</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
@@ -3643,10 +3643,10 @@
         <v>0.497795655580913</v>
       </c>
       <c r="H10">
-        <v>0.3356026753555522</v>
+        <v>0.1589696883263142</v>
       </c>
       <c r="I10">
-        <v>0.95969544087954</v>
+        <v>0.497795655580913</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
@@ -3678,10 +3678,10 @@
         <v>0.8799747781213381</v>
       </c>
       <c r="H11">
-        <v>0.3932299610771405</v>
+        <v>0.2316309263080703</v>
       </c>
       <c r="I11">
-        <v>0.95969544087954</v>
+        <v>0.8799747781213381</v>
       </c>
       <c r="J11" t="b">
         <v>0</v>
@@ -3713,10 +3713,10 @@
         <v>0.003403316967875255</v>
       </c>
       <c r="H12">
-        <v>0.3932299610771405</v>
+        <v>0.2432283212671866</v>
       </c>
       <c r="I12">
-        <v>0.06466302238962984</v>
+        <v>0.003403316967875255</v>
       </c>
       <c r="J12" t="b">
         <v>0</v>
@@ -3748,10 +3748,10 @@
         <v>0.4081553476384943</v>
       </c>
       <c r="H13">
-        <v>0.3932299610771405</v>
+        <v>0.2483557648908256</v>
       </c>
       <c r="I13">
-        <v>0.95969544087954</v>
+        <v>0.4081553476384943</v>
       </c>
       <c r="J13" t="b">
         <v>1</v>
@@ -3783,10 +3783,10 @@
         <v>0.7148771940079472</v>
       </c>
       <c r="H14">
-        <v>0.4055401192665947</v>
+        <v>0.2774748184455648</v>
       </c>
       <c r="I14">
-        <v>0.95969544087954</v>
+        <v>0.7148771940079472</v>
       </c>
       <c r="J14" t="b">
         <v>1</v>
@@ -3818,10 +3818,10 @@
         <v>0.5673721116593613</v>
       </c>
       <c r="H15">
-        <v>0.4073152161111558</v>
+        <v>0.3001270013450621</v>
       </c>
       <c r="I15">
-        <v>0.95969544087954</v>
+        <v>0.5673721116593613</v>
       </c>
       <c r="J15" t="b">
         <v>1</v>
@@ -3853,10 +3853,10 @@
         <v>0.5952231920428072</v>
       </c>
       <c r="H16">
-        <v>0.5006632604860186</v>
+        <v>0.3952604688047515</v>
       </c>
       <c r="I16">
-        <v>0.95969544087954</v>
+        <v>0.5952231920428072</v>
       </c>
       <c r="J16" t="b">
         <v>0</v>
@@ -3888,10 +3888,10 @@
         <v>0.05409631121523648</v>
       </c>
       <c r="H17">
-        <v>0.5710803399046239</v>
+        <v>0.4809097599196833</v>
       </c>
       <c r="I17">
-        <v>0.4411025270837003</v>
+        <v>0.05409631121523648</v>
       </c>
       <c r="J17" t="b">
         <v>1</v>
@@ -3923,10 +3923,10 @@
         <v>0.5350572518374678</v>
       </c>
       <c r="H18">
-        <v>0.6498613252573568</v>
+        <v>0.618470367699212</v>
       </c>
       <c r="I18">
-        <v>0.95969544087954</v>
+        <v>0.5350572518374678</v>
       </c>
       <c r="J18" t="b">
         <v>1</v>
@@ -3958,10 +3958,10 @@
         <v>0.8390647212927266</v>
       </c>
       <c r="H19">
-        <v>0.6498613252573568</v>
+        <v>0.6203920622497769</v>
       </c>
       <c r="I19">
-        <v>0.95969544087954</v>
+        <v>0.8390647212927266</v>
       </c>
       <c r="J19" t="b">
         <v>0</v>
@@ -3996,7 +3996,7 @@
         <v>0.6498613252573568</v>
       </c>
       <c r="I20">
-        <v>0.6419567155485885</v>
+        <v>0.1689359777759444</v>
       </c>
       <c r="J20" t="b">
         <v>0</v>
@@ -4012,7 +4012,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W3"/>
+  <dimension ref="A1:W7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:23" s="1" customFormat="1">
@@ -4145,10 +4145,10 @@
         <v>0.001924135753232891</v>
       </c>
       <c r="T2">
-        <v>0.03939794677721668</v>
+        <v>0.00401557133453159</v>
       </c>
       <c r="U2">
-        <v>0.05953933996031915</v>
+        <v>0.02899989459508442</v>
       </c>
       <c r="V2" t="b">
         <v>1</v>
@@ -4216,15 +4216,299 @@
         <v>0.001982944495211959</v>
       </c>
       <c r="T3">
-        <v>0.03939794677721668</v>
+        <v>0.004147152292338598</v>
       </c>
       <c r="U3">
-        <v>0.05953933996031915</v>
+        <v>0.005793488543173329</v>
       </c>
       <c r="V3" t="b">
         <v>1</v>
       </c>
       <c r="W3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4">
+        <v>19</v>
+      </c>
+      <c r="E4">
+        <v>0.07744323765729549</v>
+      </c>
+      <c r="F4">
+        <v>1.006033641552899</v>
+      </c>
+      <c r="G4">
+        <v>0.5101929833146301</v>
+      </c>
+      <c r="H4">
+        <v>0.1776564255621539</v>
+      </c>
+      <c r="I4">
+        <v>0.01106990333221139</v>
+      </c>
+      <c r="J4">
+        <v>-0.5286980752799678</v>
+      </c>
+      <c r="K4">
+        <v>0.1776564255621539</v>
+      </c>
+      <c r="L4">
+        <v>0.008915355404983626</v>
+      </c>
+      <c r="M4">
+        <v>1.720394952287141</v>
+      </c>
+      <c r="N4">
+        <v>0.5990658981486253</v>
+      </c>
+      <c r="O4">
+        <v>-3.752777077877509</v>
+      </c>
+      <c r="P4">
+        <v>1.261031565575976</v>
+      </c>
+      <c r="Q4">
+        <v>0.4980397594688339</v>
+      </c>
+      <c r="R4">
+        <v>0.4352947294024382</v>
+      </c>
+      <c r="S4">
+        <v>0.004030459392074336</v>
+      </c>
+      <c r="T4">
+        <v>0.008915355404983626</v>
+      </c>
+      <c r="U4">
+        <v>0.01106990333221139</v>
+      </c>
+      <c r="V4" t="b">
+        <v>1</v>
+      </c>
+      <c r="W4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23">
+      <c r="A5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5">
+        <v>19</v>
+      </c>
+      <c r="E5">
+        <v>0.02564454649584646</v>
+      </c>
+      <c r="F5">
+        <v>1.000658075543598</v>
+      </c>
+      <c r="G5">
+        <v>0.4802461520475643</v>
+      </c>
+      <c r="H5">
+        <v>0.1930705584009144</v>
+      </c>
+      <c r="I5">
+        <v>0.02428101019834354</v>
+      </c>
+      <c r="J5">
+        <v>-0.4288342329460387</v>
+      </c>
+      <c r="K5">
+        <v>0.1930705584009144</v>
+      </c>
+      <c r="L5">
+        <v>0.04112387770356465</v>
+      </c>
+      <c r="M5">
+        <v>1.619412816048934</v>
+      </c>
+      <c r="N5">
+        <v>0.6510430855991501</v>
+      </c>
+      <c r="O5">
+        <v>-3.653044123033042</v>
+      </c>
+      <c r="P5">
+        <v>1.644680425468546</v>
+      </c>
+      <c r="Q5">
+        <v>0.4039723828582955</v>
+      </c>
+      <c r="R5">
+        <v>0.3294689307155825</v>
+      </c>
+      <c r="S5">
+        <v>0.01592689317284809</v>
+      </c>
+      <c r="T5">
+        <v>0.04112387770356465</v>
+      </c>
+      <c r="U5">
+        <v>0.02428101019834354</v>
+      </c>
+      <c r="V5" t="b">
+        <v>1</v>
+      </c>
+      <c r="W5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23">
+      <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6">
+        <v>19</v>
+      </c>
+      <c r="E6">
+        <v>-0.005597819156339884</v>
+      </c>
+      <c r="F6">
+        <v>1.000031336561257</v>
+      </c>
+      <c r="G6">
+        <v>0.471617008805046</v>
+      </c>
+      <c r="H6">
+        <v>0.1937886799420862</v>
+      </c>
+      <c r="I6">
+        <v>0.02704165709062151</v>
+      </c>
+      <c r="J6">
+        <v>0.4230426380593251</v>
+      </c>
+      <c r="K6">
+        <v>0.1937886799420862</v>
+      </c>
+      <c r="L6">
+        <v>0.04427980316802854</v>
+      </c>
+      <c r="M6">
+        <v>1.590314935516469</v>
+      </c>
+      <c r="N6">
+        <v>0.6534646255163284</v>
+      </c>
+      <c r="O6">
+        <v>2.260920041359433</v>
+      </c>
+      <c r="P6">
+        <v>1.035689244657672</v>
+      </c>
+      <c r="Q6">
+        <v>0.3991539888686922</v>
+      </c>
+      <c r="R6">
+        <v>0.3240482374772786</v>
+      </c>
+      <c r="S6">
+        <v>0.01698656083215125</v>
+      </c>
+      <c r="T6">
+        <v>0.04427980316802854</v>
+      </c>
+      <c r="U6">
+        <v>0.02704165709062151</v>
+      </c>
+      <c r="V6" t="b">
+        <v>1</v>
+      </c>
+      <c r="W6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23">
+      <c r="A7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7">
+        <v>17</v>
+      </c>
+      <c r="E7">
+        <v>0.2212517115230526</v>
+      </c>
+      <c r="F7">
+        <v>1.051471993332927</v>
+      </c>
+      <c r="G7">
+        <v>-0.597455085703657</v>
+      </c>
+      <c r="H7">
+        <v>0.1773180937314105</v>
+      </c>
+      <c r="I7">
+        <v>0.004583616726171178</v>
+      </c>
+      <c r="J7">
+        <v>0.6240062304031372</v>
+      </c>
+      <c r="K7">
+        <v>0.1773180937314105</v>
+      </c>
+      <c r="L7">
+        <v>0.003403316967875255</v>
+      </c>
+      <c r="M7">
+        <v>-4.411999436516661</v>
+      </c>
+      <c r="N7">
+        <v>1.309432873444871</v>
+      </c>
+      <c r="O7">
+        <v>5.448492357166543</v>
+      </c>
+      <c r="P7">
+        <v>1.5482478081329</v>
+      </c>
+      <c r="Q7">
+        <v>0.581364133429465</v>
+      </c>
+      <c r="R7">
+        <v>0.5215590096336744</v>
+      </c>
+      <c r="S7">
+        <v>0.002253486890922358</v>
+      </c>
+      <c r="T7">
+        <v>0.003403316967875255</v>
+      </c>
+      <c r="U7">
+        <v>0.004583616726171178</v>
+      </c>
+      <c r="V7" t="b">
+        <v>1</v>
+      </c>
+      <c r="W7" t="b">
         <v>1</v>
       </c>
     </row>

--- a/New_Outputs/multivariable_regression/Stats_MVR_ROE_Receptor_NRS.xlsx
+++ b/New_Outputs/multivariable_regression/Stats_MVR_ROE_Receptor_NRS.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="55">
   <si>
     <t>group</t>
   </si>
@@ -96,58 +96,58 @@
     <t>nrs</t>
   </si>
   <si>
+    <t>5HTT</t>
+  </si>
+  <si>
+    <t>VAChT</t>
+  </si>
+  <si>
+    <t>M1</t>
+  </si>
+  <si>
+    <t>MOR</t>
+  </si>
+  <si>
+    <t>mGluR5</t>
+  </si>
+  <si>
     <t>5HT2A</t>
   </si>
   <si>
-    <t>mGluR5</t>
-  </si>
-  <si>
     <t>H3</t>
   </si>
   <si>
-    <t>VAChT</t>
-  </si>
-  <si>
-    <t>M1</t>
+    <t>DAT</t>
+  </si>
+  <si>
+    <t>NMDA</t>
   </si>
   <si>
     <t>D2</t>
   </si>
   <si>
-    <t>5HTT</t>
+    <t>D1</t>
+  </si>
+  <si>
+    <t>5HT1A</t>
+  </si>
+  <si>
+    <t>GABA</t>
+  </si>
+  <si>
+    <t>a4b2</t>
+  </si>
+  <si>
+    <t>5HT1B</t>
+  </si>
+  <si>
+    <t>5HT6</t>
   </si>
   <si>
     <t>NET</t>
   </si>
   <si>
-    <t>MOR</t>
-  </si>
-  <si>
-    <t>5HT6</t>
-  </si>
-  <si>
-    <t>NMDA</t>
-  </si>
-  <si>
     <t>CB1</t>
-  </si>
-  <si>
-    <t>D1</t>
-  </si>
-  <si>
-    <t>GABA</t>
-  </si>
-  <si>
-    <t>DAT</t>
-  </si>
-  <si>
-    <t>5HT1A</t>
-  </si>
-  <si>
-    <t>5HT1B</t>
-  </si>
-  <si>
-    <t>a4b2</t>
   </si>
   <si>
     <t>Tramadol group</t>
@@ -608,58 +608,58 @@
         <v>25</v>
       </c>
       <c r="D2">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E2">
-        <v>0.1072622495056885</v>
+        <v>0.1167132846248926</v>
       </c>
       <c r="F2">
-        <v>1.01163910023057</v>
+        <v>1.01381011202702</v>
       </c>
       <c r="G2">
-        <v>0.4080145151788713</v>
+        <v>0.1024484219665803</v>
       </c>
       <c r="H2">
-        <v>0.1701051819568234</v>
+        <v>0.1904435029613048</v>
       </c>
       <c r="I2">
-        <v>0.02899989459508442</v>
+        <v>0.5965501416413891</v>
       </c>
       <c r="J2">
-        <v>0.5708847029135828</v>
+        <v>0.5116398734165161</v>
       </c>
       <c r="K2">
-        <v>0.1701051819568235</v>
+        <v>0.1904435029613049</v>
       </c>
       <c r="L2">
-        <v>0.00401557133453159</v>
+        <v>0.01418859194096281</v>
       </c>
       <c r="M2">
-        <v>1.375844308585351</v>
+        <v>0.1397675755035537</v>
       </c>
       <c r="N2">
-        <v>0.5736027463473203</v>
+        <v>0.2598168538700222</v>
       </c>
       <c r="O2">
-        <v>2.58713861483516</v>
+        <v>2.397938528513136</v>
       </c>
       <c r="P2">
-        <v>0.7708836522997121</v>
+        <v>0.8925649406612035</v>
       </c>
       <c r="Q2">
-        <v>0.5423542182666672</v>
+        <v>0.2845064891361843</v>
       </c>
       <c r="R2">
-        <v>0.4851484955500006</v>
+        <v>0.2129571380498027</v>
       </c>
       <c r="S2">
-        <v>0.001924135753232891</v>
+        <v>0.03516065792606451</v>
       </c>
       <c r="T2">
-        <v>0.00401557133453159</v>
+        <v>0.01418859194096281</v>
       </c>
       <c r="U2">
-        <v>0.02899989459508442</v>
+        <v>0.5965501416413891</v>
       </c>
       <c r="V2" t="b">
         <v>1</v>
@@ -679,64 +679,64 @@
         <v>25</v>
       </c>
       <c r="D3">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E3">
-        <v>0.130591593814251</v>
+        <v>-0.2153453242937488</v>
       </c>
       <c r="F3">
-        <v>1.017350055065956</v>
+        <v>1.048628696854465</v>
       </c>
       <c r="G3">
-        <v>0.5438112914683911</v>
+        <v>0.07813361480432859</v>
       </c>
       <c r="H3">
-        <v>0.1709059272915808</v>
+        <v>0.2084212978438164</v>
       </c>
       <c r="I3">
-        <v>0.005793488543173329</v>
+        <v>0.711693254377782</v>
       </c>
       <c r="J3">
-        <v>-0.5709586403599395</v>
+        <v>-0.3902103637928717</v>
       </c>
       <c r="K3">
-        <v>0.1709059272915808</v>
+        <v>0.2084212978438164</v>
       </c>
       <c r="L3">
-        <v>0.004147152292338598</v>
+        <v>0.07587274586043942</v>
       </c>
       <c r="M3">
-        <v>1.833757482826876</v>
+        <v>0.1065955501988305</v>
       </c>
       <c r="N3">
-        <v>0.5763028976175987</v>
+        <v>0.2843434669246235</v>
       </c>
       <c r="O3">
-        <v>-2.630938139792167</v>
+        <v>-2.196913723023127</v>
       </c>
       <c r="P3">
-        <v>0.7875227567175551</v>
+        <v>1.173427596726828</v>
       </c>
       <c r="Q3">
-        <v>0.540628740906665</v>
+        <v>0.1715001215357811</v>
       </c>
       <c r="R3">
-        <v>0.4832073335199981</v>
+        <v>0.08865013368935915</v>
       </c>
       <c r="S3">
-        <v>0.001982944495211959</v>
+        <v>0.1523787794173723</v>
       </c>
       <c r="T3">
-        <v>0.004147152292338598</v>
+        <v>0.07587274586043942</v>
       </c>
       <c r="U3">
-        <v>0.005793488543173329</v>
+        <v>0.711693254377782</v>
       </c>
       <c r="V3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:23">
@@ -750,64 +750,64 @@
         <v>25</v>
       </c>
       <c r="D4">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E4">
-        <v>0.07744323765729549</v>
+        <v>0.2986680549588593</v>
       </c>
       <c r="F4">
-        <v>1.006033641552899</v>
+        <v>1.097939023259907</v>
       </c>
       <c r="G4">
-        <v>0.5101929833146301</v>
+        <v>0.05696608567286646</v>
       </c>
       <c r="H4">
-        <v>0.1776564255621539</v>
+        <v>0.2173713457953005</v>
       </c>
       <c r="I4">
-        <v>0.01106990333221139</v>
+        <v>0.7959492044855347</v>
       </c>
       <c r="J4">
-        <v>-0.5286980752799678</v>
+        <v>0.352222156734206</v>
       </c>
       <c r="K4">
-        <v>0.1776564255621539</v>
+        <v>0.2173713457953005</v>
       </c>
       <c r="L4">
-        <v>0.008915355404983626</v>
+        <v>0.1208134706567315</v>
       </c>
       <c r="M4">
-        <v>1.720394952287141</v>
+        <v>0.07771727009149611</v>
       </c>
       <c r="N4">
-        <v>0.5990658981486253</v>
+        <v>0.2965537721573147</v>
       </c>
       <c r="O4">
-        <v>-3.752777077877509</v>
+        <v>1.879047874824789</v>
       </c>
       <c r="P4">
-        <v>1.261031565575976</v>
+        <v>1.159640748190323</v>
       </c>
       <c r="Q4">
-        <v>0.4980397594688339</v>
+        <v>0.1392909629431233</v>
       </c>
       <c r="R4">
-        <v>0.4352947294024382</v>
+        <v>0.05322005923743556</v>
       </c>
       <c r="S4">
-        <v>0.004030459392074336</v>
+        <v>0.223132909748369</v>
       </c>
       <c r="T4">
-        <v>0.008915355404983626</v>
+        <v>0.1208134706567315</v>
       </c>
       <c r="U4">
-        <v>0.01106990333221139</v>
+        <v>0.7959492044855347</v>
       </c>
       <c r="V4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:23">
@@ -821,64 +821,64 @@
         <v>25</v>
       </c>
       <c r="D5">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E5">
-        <v>0.02564454649584646</v>
+        <v>0.4050592968718019</v>
       </c>
       <c r="F5">
-        <v>1.000658075543598</v>
+        <v>1.196276757004152</v>
       </c>
       <c r="G5">
-        <v>0.4802461520475643</v>
+        <v>0.02129536541002049</v>
       </c>
       <c r="H5">
-        <v>0.1930705584009144</v>
+        <v>0.2284592918956312</v>
       </c>
       <c r="I5">
-        <v>0.02428101019834354</v>
+        <v>0.9266618344992273</v>
       </c>
       <c r="J5">
-        <v>-0.4288342329460387</v>
+        <v>0.3477718640603116</v>
       </c>
       <c r="K5">
-        <v>0.1930705584009144</v>
+        <v>0.2284592918956312</v>
       </c>
       <c r="L5">
-        <v>0.04112387770356465</v>
+        <v>0.1436017312656375</v>
       </c>
       <c r="M5">
-        <v>1.619412816048934</v>
+        <v>0.02905268364008337</v>
       </c>
       <c r="N5">
-        <v>0.6510430855991501</v>
+        <v>0.3116807532665291</v>
       </c>
       <c r="O5">
-        <v>-3.653044123033042</v>
+        <v>2.708114782145101</v>
       </c>
       <c r="P5">
-        <v>1.644680425468546</v>
+        <v>1.779022541609822</v>
       </c>
       <c r="Q5">
-        <v>0.4039723828582955</v>
+        <v>0.1273984427456018</v>
       </c>
       <c r="R5">
-        <v>0.3294689307155825</v>
+        <v>0.04013828702016198</v>
       </c>
       <c r="S5">
-        <v>0.01592689317284809</v>
+        <v>0.2559527717689384</v>
       </c>
       <c r="T5">
-        <v>0.04112387770356465</v>
+        <v>0.1436017312656375</v>
       </c>
       <c r="U5">
-        <v>0.02428101019834354</v>
+        <v>0.9266618344992273</v>
       </c>
       <c r="V5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:23">
@@ -892,64 +892,64 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E6">
-        <v>-0.005597819156339884</v>
+        <v>0.39780539513957</v>
       </c>
       <c r="F6">
-        <v>1.000031336561257</v>
+        <v>1.18799996352098</v>
       </c>
       <c r="G6">
-        <v>0.471617008805046</v>
+        <v>0.2962873518148167</v>
       </c>
       <c r="H6">
-        <v>0.1937886799420862</v>
+        <v>0.2283728034919489</v>
       </c>
       <c r="I6">
-        <v>0.02704165709062151</v>
+        <v>0.2092652619415086</v>
       </c>
       <c r="J6">
-        <v>0.4230426380593251</v>
+        <v>-0.3371592273897476</v>
       </c>
       <c r="K6">
-        <v>0.1937886799420862</v>
+        <v>0.228372803491949</v>
       </c>
       <c r="L6">
-        <v>0.04427980316802854</v>
+        <v>0.1554211973383916</v>
       </c>
       <c r="M6">
-        <v>1.590314935516469</v>
+        <v>0.4042167172573347</v>
       </c>
       <c r="N6">
-        <v>0.6534646255163284</v>
+        <v>0.3115627595067444</v>
       </c>
       <c r="O6">
-        <v>2.260920041359433</v>
+        <v>-1.539250999633476</v>
       </c>
       <c r="P6">
-        <v>1.035689244657672</v>
+        <v>1.04260253763641</v>
       </c>
       <c r="Q6">
-        <v>0.3991539888686922</v>
+        <v>0.1219841923193578</v>
       </c>
       <c r="R6">
-        <v>0.3240482374772786</v>
+        <v>0.03418261155129354</v>
       </c>
       <c r="S6">
-        <v>0.01698656083215125</v>
+        <v>0.2722847696337591</v>
       </c>
       <c r="T6">
-        <v>0.04427980316802854</v>
+        <v>0.1554211973383916</v>
       </c>
       <c r="U6">
-        <v>0.02704165709062151</v>
+        <v>0.2092652619415086</v>
       </c>
       <c r="V6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:23">
@@ -963,58 +963,58 @@
         <v>25</v>
       </c>
       <c r="D7">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E7">
-        <v>0.08727567879813293</v>
+        <v>-0.1464030468939358</v>
       </c>
       <c r="F7">
-        <v>1.007675508798759</v>
+        <v>1.021903324764194</v>
       </c>
       <c r="G7">
-        <v>0.4348932093812352</v>
+        <v>0.1168488734897196</v>
       </c>
       <c r="H7">
-        <v>0.1985626562947616</v>
+        <v>0.21204097129914</v>
       </c>
       <c r="I7">
-        <v>0.04366733272239159</v>
+        <v>0.5876914274750935</v>
       </c>
       <c r="J7">
-        <v>0.3936455575441325</v>
+        <v>-0.3095203249505835</v>
       </c>
       <c r="K7">
-        <v>0.1985626562947616</v>
+        <v>0.21204097129914</v>
       </c>
       <c r="L7">
-        <v>0.06486872221967133</v>
+        <v>0.1598970911204966</v>
       </c>
       <c r="M7">
-        <v>1.466480541034866</v>
+        <v>0.1594137170146664</v>
       </c>
       <c r="N7">
-        <v>0.6695627003391567</v>
+        <v>0.289281688258381</v>
       </c>
       <c r="O7">
-        <v>3.153555043003871</v>
+        <v>-2.196358071215989</v>
       </c>
       <c r="P7">
-        <v>1.590715947659049</v>
+        <v>1.504643996531401</v>
       </c>
       <c r="Q7">
-        <v>0.3739710352300636</v>
+        <v>0.1200464384464618</v>
       </c>
       <c r="R7">
-        <v>0.2957174146338215</v>
+        <v>0.03205108229110798</v>
       </c>
       <c r="S7">
-        <v>0.02359149260414747</v>
+        <v>0.2783540432608901</v>
       </c>
       <c r="T7">
-        <v>0.06486872221967133</v>
+        <v>0.1598970911204966</v>
       </c>
       <c r="U7">
-        <v>0.04366733272239159</v>
+        <v>0.5876914274750935</v>
       </c>
       <c r="V7" t="b">
         <v>0</v>
@@ -1034,58 +1034,58 @@
         <v>25</v>
       </c>
       <c r="D8">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E8">
-        <v>-0.08567135329026582</v>
+        <v>-0.242960532853509</v>
       </c>
       <c r="F8">
-        <v>1.007393848523056</v>
+        <v>1.062732934382004</v>
       </c>
       <c r="G8">
-        <v>0.4398563360089229</v>
+        <v>0.09455557519642897</v>
       </c>
       <c r="H8">
-        <v>0.2043073542734493</v>
+        <v>0.2187868162725794</v>
       </c>
       <c r="I8">
-        <v>0.04692806961885894</v>
+        <v>0.6702334617212731</v>
       </c>
       <c r="J8">
-        <v>-0.3430850043101364</v>
+        <v>-0.2782674871001408</v>
       </c>
       <c r="K8">
-        <v>0.2043073542734493</v>
+        <v>0.2187868162725794</v>
       </c>
       <c r="L8">
-        <v>0.1125200626143513</v>
+        <v>0.218011724208487</v>
       </c>
       <c r="M8">
-        <v>1.48321643956166</v>
+        <v>0.1289995808804157</v>
       </c>
       <c r="N8">
-        <v>0.6889340945530469</v>
+        <v>0.2984848597525014</v>
       </c>
       <c r="O8">
-        <v>-2.668058901835666</v>
+        <v>-1.126065499555373</v>
       </c>
       <c r="P8">
-        <v>1.588830897391875</v>
+        <v>0.8853649706961658</v>
       </c>
       <c r="Q8">
-        <v>0.3370379210250035</v>
+        <v>0.09915898103737128</v>
       </c>
       <c r="R8">
-        <v>0.2541676611531289</v>
+        <v>0.009074879141108383</v>
       </c>
       <c r="S8">
-        <v>0.03731723881839773</v>
+        <v>0.3519504554514557</v>
       </c>
       <c r="T8">
-        <v>0.1125200626143513</v>
+        <v>0.218011724208487</v>
       </c>
       <c r="U8">
-        <v>0.04692806961885894</v>
+        <v>0.6702334617212731</v>
       </c>
       <c r="V8" t="b">
         <v>0</v>
@@ -1105,58 +1105,58 @@
         <v>25</v>
       </c>
       <c r="D9">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E9">
-        <v>-0.1559373052982495</v>
+        <v>-0.06037634749681988</v>
       </c>
       <c r="F9">
-        <v>1.024922468984744</v>
+        <v>1.003658640190352</v>
       </c>
       <c r="G9">
-        <v>0.419239033426925</v>
+        <v>0.147792411569857</v>
       </c>
       <c r="H9">
-        <v>0.2086247403204231</v>
+        <v>0.2145470467652081</v>
       </c>
       <c r="I9">
-        <v>0.06165691396851415</v>
+        <v>0.4988267558457495</v>
       </c>
       <c r="J9">
-        <v>-0.3207049082911491</v>
+        <v>-0.2380266638187422</v>
       </c>
       <c r="K9">
-        <v>0.2086247403204231</v>
+        <v>0.2145470467652081</v>
       </c>
       <c r="L9">
-        <v>0.1437753082918942</v>
+        <v>0.2804036261896344</v>
       </c>
       <c r="M9">
-        <v>1.41369391680683</v>
+        <v>0.2016291383158703</v>
       </c>
       <c r="N9">
-        <v>0.7034925251963555</v>
+        <v>0.2927006583625329</v>
       </c>
       <c r="O9">
-        <v>-1.756839161530199</v>
+        <v>-2.010094832121285</v>
       </c>
       <c r="P9">
-        <v>1.142857824696108</v>
+        <v>1.811813445732423</v>
       </c>
       <c r="Q9">
-        <v>0.3205451754121028</v>
+        <v>0.08274719247288354</v>
       </c>
       <c r="R9">
-        <v>0.2356133223386156</v>
+        <v>-0.008978088279828267</v>
       </c>
       <c r="S9">
-        <v>0.04542392877196608</v>
+        <v>0.4215901904650216</v>
       </c>
       <c r="T9">
-        <v>0.1437753082918942</v>
+        <v>0.2804036261896344</v>
       </c>
       <c r="U9">
-        <v>0.06165691396851415</v>
+        <v>0.4988267558457495</v>
       </c>
       <c r="V9" t="b">
         <v>0</v>
@@ -1176,58 +1176,58 @@
         <v>25</v>
       </c>
       <c r="D10">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E10">
-        <v>0.06357971404854676</v>
+        <v>-0.09754959235810096</v>
       </c>
       <c r="F10">
-        <v>1.004058787198848</v>
+        <v>1.009607345731148</v>
       </c>
       <c r="G10">
-        <v>0.4887415759720238</v>
+        <v>0.1815119015553005</v>
       </c>
       <c r="H10">
-        <v>0.207511331959648</v>
+        <v>0.2172231111421103</v>
       </c>
       <c r="I10">
-        <v>0.03160548983618443</v>
+        <v>0.4132509352921835</v>
       </c>
       <c r="J10">
-        <v>-0.3065865212191919</v>
+        <v>0.1983433138929727</v>
       </c>
       <c r="K10">
-        <v>0.2075113319596481</v>
+        <v>0.2172231111421103</v>
       </c>
       <c r="L10">
-        <v>0.1589696883263142</v>
+        <v>0.3720738204606681</v>
       </c>
       <c r="M10">
-        <v>1.648059788694904</v>
+        <v>0.2476317147539845</v>
       </c>
       <c r="N10">
-        <v>0.6997380593640992</v>
+        <v>0.2963515396808713</v>
       </c>
       <c r="O10">
-        <v>-3.408937812136872</v>
+        <v>1.649149931624918</v>
       </c>
       <c r="P10">
-        <v>2.307320045092212</v>
+        <v>1.806128333020937</v>
       </c>
       <c r="Q10">
-        <v>0.3138098535158492</v>
+        <v>0.06526274370386963</v>
       </c>
       <c r="R10">
-        <v>0.2280360852053304</v>
+        <v>-0.02821098192574345</v>
       </c>
       <c r="S10">
-        <v>0.04915365526352789</v>
+        <v>0.509208364885372</v>
       </c>
       <c r="T10">
-        <v>0.1589696883263142</v>
+        <v>0.3720738204606681</v>
       </c>
       <c r="U10">
-        <v>0.03160548983618443</v>
+        <v>0.4132509352921835</v>
       </c>
       <c r="V10" t="b">
         <v>0</v>
@@ -1247,58 +1247,58 @@
         <v>25</v>
       </c>
       <c r="D11">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E11">
-        <v>0.1282776791981364</v>
+        <v>0.1008439161286934</v>
       </c>
       <c r="F11">
-        <v>1.016730465517286</v>
+        <v>1.010273976577927</v>
       </c>
       <c r="G11">
-        <v>0.5031543265768557</v>
+        <v>0.1430735452338817</v>
       </c>
       <c r="H11">
-        <v>0.2125721529631003</v>
+        <v>0.2177006176704028</v>
       </c>
       <c r="I11">
-        <v>0.03087957842271282</v>
+        <v>0.5185425562568738</v>
       </c>
       <c r="J11">
-        <v>-0.2643128108259331</v>
+        <v>0.1893029112419877</v>
       </c>
       <c r="K11">
-        <v>0.2125721529631003</v>
+        <v>0.2177006176704029</v>
       </c>
       <c r="L11">
-        <v>0.2316309263080703</v>
+        <v>0.394859379083636</v>
       </c>
       <c r="M11">
-        <v>1.696660267729392</v>
+        <v>0.1951913182475459</v>
       </c>
       <c r="N11">
-        <v>0.7168033879623145</v>
+        <v>0.2970029887560786</v>
       </c>
       <c r="O11">
-        <v>-1.34037913953689</v>
+        <v>1.854574358085141</v>
       </c>
       <c r="P11">
-        <v>1.07799269580553</v>
+        <v>2.132782748146536</v>
       </c>
       <c r="Q11">
-        <v>0.2889062067417794</v>
+        <v>0.06176819292901474</v>
       </c>
       <c r="R11">
-        <v>0.2000194825845018</v>
+        <v>-0.03205498777808402</v>
       </c>
       <c r="S11">
-        <v>0.06537551205920639</v>
+        <v>0.5285687936852966</v>
       </c>
       <c r="T11">
-        <v>0.2316309263080703</v>
+        <v>0.394859379083636</v>
       </c>
       <c r="U11">
-        <v>0.03087957842271282</v>
+        <v>0.5185425562568738</v>
       </c>
       <c r="V11" t="b">
         <v>0</v>
@@ -1318,58 +1318,58 @@
         <v>25</v>
       </c>
       <c r="D12">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E12">
-        <v>-0.08894236834942722</v>
+        <v>0.1091225672421233</v>
       </c>
       <c r="F12">
-        <v>1.007973823773254</v>
+        <v>1.012051237621695</v>
       </c>
       <c r="G12">
-        <v>0.492109569667527</v>
+        <v>0.181661308054391</v>
       </c>
       <c r="H12">
-        <v>0.2121261604320802</v>
+        <v>0.218347400911194</v>
       </c>
       <c r="I12">
-        <v>0.0338921169339256</v>
+        <v>0.4152425381688637</v>
       </c>
       <c r="J12">
-        <v>0.257027977442039</v>
+        <v>-0.1786772104897687</v>
       </c>
       <c r="K12">
-        <v>0.2121261604320802</v>
+        <v>0.218347400911194</v>
       </c>
       <c r="L12">
-        <v>0.2432283212671866</v>
+        <v>0.4228199328322441</v>
       </c>
       <c r="M12">
-        <v>1.659416823273141</v>
+        <v>0.2478355459476866</v>
       </c>
       <c r="N12">
-        <v>0.7152994799819661</v>
+        <v>0.297885377412794</v>
       </c>
       <c r="O12">
-        <v>1.771794170495995</v>
+        <v>-1.301194655038986</v>
       </c>
       <c r="P12">
-        <v>1.462268419973902</v>
+        <v>1.590087903367896</v>
       </c>
       <c r="Q12">
-        <v>0.2857352938597115</v>
+        <v>0.05784241523757987</v>
       </c>
       <c r="R12">
-        <v>0.1964522055921755</v>
+        <v>-0.03637334323866237</v>
       </c>
       <c r="S12">
-        <v>0.06774441976825889</v>
+        <v>0.5511064415485325</v>
       </c>
       <c r="T12">
-        <v>0.2432283212671866</v>
+        <v>0.4228199328322441</v>
       </c>
       <c r="U12">
-        <v>0.0338921169339256</v>
+        <v>0.4152425381688637</v>
       </c>
       <c r="V12" t="b">
         <v>0</v>
@@ -1389,58 +1389,58 @@
         <v>25</v>
       </c>
       <c r="D13">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E13">
-        <v>-0.1814450755120865</v>
+        <v>-0.2268495408188149</v>
       </c>
       <c r="F13">
-        <v>1.034043092869156</v>
+        <v>1.054252591261585</v>
       </c>
       <c r="G13">
-        <v>0.5159962642083163</v>
+        <v>0.1910572549232155</v>
       </c>
       <c r="H13">
-        <v>0.2150544245647966</v>
+        <v>0.2247560838987512</v>
       </c>
       <c r="I13">
-        <v>0.02895526728386478</v>
+        <v>0.4053508181863821</v>
       </c>
       <c r="J13">
-        <v>0.2576392412668895</v>
+        <v>0.1273692804527506</v>
       </c>
       <c r="K13">
-        <v>0.2150544245647966</v>
+        <v>0.2247560838987513</v>
       </c>
       <c r="L13">
-        <v>0.2483557648908256</v>
+        <v>0.5772231580489248</v>
       </c>
       <c r="M13">
-        <v>1.739963890870612</v>
+        <v>0.2606541788578567</v>
       </c>
       <c r="N13">
-        <v>0.7251737256059635</v>
+        <v>0.3066285680461641</v>
       </c>
       <c r="O13">
-        <v>2.444788354111304</v>
+        <v>0.7500203294478585</v>
       </c>
       <c r="P13">
-        <v>2.04069283114944</v>
+        <v>1.323487354972425</v>
       </c>
       <c r="Q13">
-        <v>0.2843871851170843</v>
+        <v>0.04168512046903829</v>
       </c>
       <c r="R13">
-        <v>0.1949355832567198</v>
+        <v>-0.05414636748405788</v>
       </c>
       <c r="S13">
-        <v>0.06877409322085867</v>
+        <v>0.65325435531287</v>
       </c>
       <c r="T13">
-        <v>0.2483557648908256</v>
+        <v>0.5772231580489248</v>
       </c>
       <c r="U13">
-        <v>0.02895526728386478</v>
+        <v>0.4053508181863821</v>
       </c>
       <c r="V13" t="b">
         <v>0</v>
@@ -1460,58 +1460,58 @@
         <v>25</v>
       </c>
       <c r="D14">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E14">
-        <v>-0.2789675381454208</v>
+        <v>-0.1789851784738659</v>
       </c>
       <c r="F14">
-        <v>1.084390391249623</v>
+        <v>1.033095945706362</v>
       </c>
       <c r="G14">
-        <v>0.5386629128754358</v>
+        <v>0.1400923989010339</v>
       </c>
       <c r="H14">
-        <v>0.2213170553118759</v>
+        <v>0.2225671249754876</v>
       </c>
       <c r="I14">
-        <v>0.02702920595243895</v>
+        <v>0.5361864343544274</v>
       </c>
       <c r="J14">
-        <v>0.2488247224574301</v>
+        <v>-0.1233129660525213</v>
       </c>
       <c r="K14">
-        <v>0.221317055311876</v>
+        <v>0.2225671249754876</v>
       </c>
       <c r="L14">
-        <v>0.2774748184455648</v>
+        <v>0.5856879393918062</v>
       </c>
       <c r="M14">
-        <v>1.816396905881581</v>
+        <v>0.1911242219744635</v>
       </c>
       <c r="N14">
-        <v>0.7462916136947325</v>
+        <v>0.3036422313539189</v>
       </c>
       <c r="O14">
-        <v>1.819288275161559</v>
+        <v>-0.7633486139683703</v>
       </c>
       <c r="P14">
-        <v>1.618165268489602</v>
+        <v>1.37776514346919</v>
       </c>
       <c r="Q14">
-        <v>0.2772899595249972</v>
+        <v>0.04101598064089056</v>
       </c>
       <c r="R14">
-        <v>0.1869512044656217</v>
+        <v>-0.05488242129502052</v>
       </c>
       <c r="S14">
-        <v>0.07442394836772885</v>
+        <v>0.657830038636472</v>
       </c>
       <c r="T14">
-        <v>0.2774748184455648</v>
+        <v>0.5856879393918062</v>
       </c>
       <c r="U14">
-        <v>0.02702920595243895</v>
+        <v>0.5361864343544274</v>
       </c>
       <c r="V14" t="b">
         <v>0</v>
@@ -1531,58 +1531,58 @@
         <v>25</v>
       </c>
       <c r="D15">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E15">
-        <v>0.1932910373363649</v>
+        <v>0.558509287373361</v>
       </c>
       <c r="F15">
-        <v>1.038811477214088</v>
+        <v>1.453346045750627</v>
       </c>
       <c r="G15">
-        <v>0.4242595336725857</v>
+        <v>0.09060138773901065</v>
       </c>
       <c r="H15">
-        <v>0.2173557311062607</v>
+        <v>0.2644531977063777</v>
       </c>
       <c r="I15">
-        <v>0.06867714314795682</v>
+        <v>0.7354746130182958</v>
       </c>
       <c r="J15">
-        <v>0.2327545010319998</v>
+        <v>0.1281307330369182</v>
       </c>
       <c r="K15">
-        <v>0.2173557311062607</v>
+        <v>0.2644531977063777</v>
       </c>
       <c r="L15">
-        <v>0.3001270013450621</v>
+        <v>0.6332863400645941</v>
       </c>
       <c r="M15">
-        <v>1.430623281896245</v>
+        <v>0.1236049912576472</v>
       </c>
       <c r="N15">
-        <v>0.7329338404783365</v>
+        <v>0.3607862529072399</v>
       </c>
       <c r="O15">
-        <v>1.664219425870941</v>
+        <v>0.7762655272918955</v>
       </c>
       <c r="P15">
-        <v>1.554116583900943</v>
+        <v>1.602159732454041</v>
       </c>
       <c r="Q15">
-        <v>0.2723451385587533</v>
+        <v>0.03759336626525052</v>
       </c>
       <c r="R15">
-        <v>0.1813882808785975</v>
+        <v>-0.05864729710822436</v>
       </c>
       <c r="S15">
-        <v>0.07859654973329193</v>
+        <v>0.6816886744939537</v>
       </c>
       <c r="T15">
-        <v>0.3001270013450621</v>
+        <v>0.6332863400645941</v>
       </c>
       <c r="U15">
-        <v>0.06867714314795682</v>
+        <v>0.7354746130182958</v>
       </c>
       <c r="V15" t="b">
         <v>0</v>
@@ -1602,58 +1602,58 @@
         <v>25</v>
       </c>
       <c r="D16">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E16">
-        <v>0.02613957325336378</v>
+        <v>0.007404521441708138</v>
       </c>
       <c r="F16">
-        <v>1.000683744476941</v>
+        <v>1.000054829943939</v>
       </c>
       <c r="G16">
-        <v>0.4643219978835769</v>
+        <v>0.1627744160135578</v>
       </c>
       <c r="H16">
-        <v>0.2157562856824031</v>
+        <v>0.2198807861680371</v>
       </c>
       <c r="I16">
-        <v>0.04700474207393617</v>
+        <v>0.4677293926969883</v>
       </c>
       <c r="J16">
-        <v>0.1884841305723298</v>
+        <v>-0.08249336304585529</v>
       </c>
       <c r="K16">
-        <v>0.2157562856824032</v>
+        <v>0.2198807861680372</v>
       </c>
       <c r="L16">
-        <v>0.3952604688047515</v>
+        <v>0.7114809024930642</v>
       </c>
       <c r="M16">
-        <v>1.56571581248534</v>
+        <v>0.2220686765448008</v>
       </c>
       <c r="N16">
-        <v>0.7275404346031986</v>
+        <v>0.2999773329114523</v>
       </c>
       <c r="O16">
-        <v>1.321789105587023</v>
+        <v>-0.8577767417584192</v>
       </c>
       <c r="P16">
-        <v>1.513041479996025</v>
+        <v>2.286349075496628</v>
       </c>
       <c r="Q16">
-        <v>0.2556965164126024</v>
+        <v>0.03310181245593603</v>
       </c>
       <c r="R16">
-        <v>0.1626585809641776</v>
+        <v>-0.06358800629847039</v>
       </c>
       <c r="S16">
-        <v>0.09418904924723714</v>
+        <v>0.7141796340620227</v>
       </c>
       <c r="T16">
-        <v>0.3952604688047515</v>
+        <v>0.7114809024930642</v>
       </c>
       <c r="U16">
-        <v>0.04700474207393617</v>
+        <v>0.4677293926969883</v>
       </c>
       <c r="V16" t="b">
         <v>0</v>
@@ -1673,58 +1673,58 @@
         <v>25</v>
       </c>
       <c r="D17">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E17">
-        <v>0.09912912589825255</v>
+        <v>-0.5111120762417438</v>
       </c>
       <c r="F17">
-        <v>1.009924103635393</v>
+        <v>1.353611433338971</v>
       </c>
       <c r="G17">
-        <v>0.4536295186613753</v>
+        <v>0.2072219130025514</v>
       </c>
       <c r="H17">
-        <v>0.2183342222246886</v>
+        <v>0.2559534861763539</v>
       </c>
       <c r="I17">
-        <v>0.05419800954467249</v>
+        <v>0.4276934544584861</v>
       </c>
       <c r="J17">
-        <v>0.1575659405735668</v>
+        <v>0.08815741783247108</v>
       </c>
       <c r="K17">
-        <v>0.2183342222246887</v>
+        <v>0.255953486176354</v>
       </c>
       <c r="L17">
-        <v>0.4809097599196833</v>
+        <v>0.7341200683749995</v>
       </c>
       <c r="M17">
-        <v>1.529660265108346</v>
+        <v>0.2827071790429614</v>
       </c>
       <c r="N17">
-        <v>0.7362333589665457</v>
+        <v>0.3491903293173329</v>
       </c>
       <c r="O17">
-        <v>1.404300207788787</v>
+        <v>0.7102797566371669</v>
       </c>
       <c r="P17">
-        <v>1.945895112366501</v>
+        <v>2.06220400213235</v>
       </c>
       <c r="Q17">
-        <v>0.2447775840126747</v>
+        <v>0.03203850865489139</v>
       </c>
       <c r="R17">
-        <v>0.150374782014259</v>
+        <v>-0.06475764047961952</v>
       </c>
       <c r="S17">
-        <v>0.1058276068550141</v>
+        <v>0.7220724913110614</v>
       </c>
       <c r="T17">
-        <v>0.4809097599196833</v>
+        <v>0.7341200683749995</v>
       </c>
       <c r="U17">
-        <v>0.05419800954467249</v>
+        <v>0.4276934544584861</v>
       </c>
       <c r="V17" t="b">
         <v>0</v>
@@ -1744,58 +1744,58 @@
         <v>25</v>
       </c>
       <c r="D18">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E18">
-        <v>0.05620973326022353</v>
+        <v>-0.03499378396413862</v>
       </c>
       <c r="F18">
-        <v>1.003169548409509</v>
+        <v>1.001226066313922</v>
       </c>
       <c r="G18">
-        <v>0.4755109377792542</v>
+        <v>0.1645988977848254</v>
       </c>
       <c r="H18">
-        <v>0.2193550253949048</v>
+        <v>0.2202332484901988</v>
       </c>
       <c r="I18">
-        <v>0.04560325889351385</v>
+        <v>0.4635288488096573</v>
       </c>
       <c r="J18">
-        <v>-0.1114049968622884</v>
+        <v>0.06959252103844972</v>
       </c>
       <c r="K18">
-        <v>0.2193550253949048</v>
+        <v>0.2202332484901988</v>
       </c>
       <c r="L18">
-        <v>0.618470367699212</v>
+        <v>0.7552806267536643</v>
       </c>
       <c r="M18">
-        <v>1.603445448814142</v>
+        <v>0.2245577670434684</v>
       </c>
       <c r="N18">
-        <v>0.7396755557014147</v>
+        <v>0.3004581876018346</v>
       </c>
       <c r="O18">
-        <v>-0.708924242572316</v>
+        <v>0.4653703778267558</v>
       </c>
       <c r="P18">
-        <v>1.395862839301016</v>
+        <v>1.47271615585347</v>
       </c>
       <c r="Q18">
-        <v>0.2325663833430886</v>
+        <v>0.03113421888602165</v>
       </c>
       <c r="R18">
-        <v>0.1366371812609748</v>
+        <v>-0.06575235922537637</v>
       </c>
       <c r="S18">
-        <v>0.1203168776218692</v>
+        <v>0.7288466726527361</v>
       </c>
       <c r="T18">
-        <v>0.618470367699212</v>
+        <v>0.7552806267536643</v>
       </c>
       <c r="U18">
-        <v>0.04560325889351385</v>
+        <v>0.4635288488096573</v>
       </c>
       <c r="V18" t="b">
         <v>0</v>
@@ -1815,58 +1815,58 @@
         <v>25</v>
       </c>
       <c r="D19">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E19">
-        <v>-0.2500616343494676</v>
+        <v>-0.5230738423154268</v>
       </c>
       <c r="F19">
-        <v>1.066701735238339</v>
+        <v>1.37666381690162</v>
       </c>
       <c r="G19">
-        <v>0.4978197020640046</v>
+        <v>0.1201859131572134</v>
       </c>
       <c r="H19">
-        <v>0.2262141731700557</v>
+        <v>0.2582654909251463</v>
       </c>
       <c r="I19">
-        <v>0.04279187982902813</v>
+        <v>0.6467024021498884</v>
       </c>
       <c r="J19">
-        <v>0.1142550696213848</v>
+        <v>-0.08025191776949758</v>
       </c>
       <c r="K19">
-        <v>0.2262141731700557</v>
+        <v>0.2582654909251464</v>
       </c>
       <c r="L19">
-        <v>0.6203920622497769</v>
+        <v>0.7592179371724763</v>
       </c>
       <c r="M19">
-        <v>1.678671660703418</v>
+        <v>0.1639663488144706</v>
       </c>
       <c r="N19">
-        <v>0.7628049275181258</v>
+        <v>0.3523445340584936</v>
       </c>
       <c r="O19">
-        <v>0.9761305752160735</v>
+        <v>-0.6854993286217427</v>
       </c>
       <c r="P19">
-        <v>1.93264571725564</v>
+        <v>2.206063425722183</v>
       </c>
       <c r="Q19">
-        <v>0.2324324530087596</v>
+        <v>0.03097527538818861</v>
       </c>
       <c r="R19">
-        <v>0.1364865096348545</v>
+        <v>-0.06592719707299266</v>
       </c>
       <c r="S19">
-        <v>0.1204849591379604</v>
+        <v>0.7300432367154993</v>
       </c>
       <c r="T19">
-        <v>0.6203920622497769</v>
+        <v>0.7592179371724763</v>
       </c>
       <c r="U19">
-        <v>0.04279187982902813</v>
+        <v>0.6467024021498884</v>
       </c>
       <c r="V19" t="b">
         <v>0</v>
@@ -1886,58 +1886,58 @@
         <v>25</v>
       </c>
       <c r="D20">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E20">
-        <v>-0.0510425531843141</v>
+        <v>-0.3081442160662443</v>
       </c>
       <c r="F20">
-        <v>1.002612147774496</v>
+        <v>1.104914819878049</v>
       </c>
       <c r="G20">
-        <v>0.4640635520158273</v>
+        <v>0.1802343220569947</v>
       </c>
       <c r="H20">
-        <v>0.2195908416658323</v>
+        <v>0.2315620599916842</v>
       </c>
       <c r="I20">
-        <v>0.05063547171003746</v>
+        <v>0.4454791702314983</v>
       </c>
       <c r="J20">
-        <v>-0.1015885821231817</v>
+        <v>0.05864374204260177</v>
       </c>
       <c r="K20">
-        <v>0.2195908416658323</v>
+        <v>0.2315620599916843</v>
       </c>
       <c r="L20">
-        <v>0.6498613252573568</v>
+        <v>0.8026578492961218</v>
       </c>
       <c r="M20">
-        <v>1.564844320754061</v>
+        <v>0.2458887480438725</v>
       </c>
       <c r="N20">
-        <v>0.7404707393582634</v>
+        <v>0.3159137747793113</v>
       </c>
       <c r="O20">
-        <v>-0.980995408475663</v>
+        <v>0.439588236598265</v>
       </c>
       <c r="P20">
-        <v>2.12049034365183</v>
+        <v>1.735768456604619</v>
       </c>
       <c r="Q20">
-        <v>0.2304878754873554</v>
+        <v>0.02940956781608467</v>
       </c>
       <c r="R20">
-        <v>0.1342988599232748</v>
+        <v>-0.06764947540230692</v>
       </c>
       <c r="S20">
-        <v>0.1229486419651181</v>
+        <v>0.741925090656077</v>
       </c>
       <c r="T20">
-        <v>0.6498613252573568</v>
+        <v>0.8026578492961218</v>
       </c>
       <c r="U20">
-        <v>0.05063547171003746</v>
+        <v>0.4454791702314983</v>
       </c>
       <c r="V20" t="b">
         <v>0</v>
@@ -1951,64 +1951,64 @@
         <v>44</v>
       </c>
       <c r="B21" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C21" t="s">
         <v>25</v>
       </c>
       <c r="D21">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E21">
-        <v>0.2212517115230526</v>
+        <v>0.1710408821198426</v>
       </c>
       <c r="F21">
-        <v>1.051471993332927</v>
+        <v>1.030136629964357</v>
       </c>
       <c r="G21">
-        <v>-0.597455085703657</v>
+        <v>0.09522523274896059</v>
       </c>
       <c r="H21">
-        <v>0.1773180937314105</v>
+        <v>0.2108328182532421</v>
       </c>
       <c r="I21">
-        <v>0.004583616726171178</v>
+        <v>0.6569071673660187</v>
       </c>
       <c r="J21">
-        <v>0.6240062304031372</v>
+        <v>0.446849729174709</v>
       </c>
       <c r="K21">
-        <v>0.1773180937314105</v>
+        <v>0.2108328182532422</v>
       </c>
       <c r="L21">
-        <v>0.003403316967875255</v>
+        <v>0.04821445347274776</v>
       </c>
       <c r="M21">
-        <v>-4.411999436516661</v>
+        <v>0.2116238289062774</v>
       </c>
       <c r="N21">
-        <v>1.309432873444871</v>
+        <v>0.4685443865017951</v>
       </c>
       <c r="O21">
-        <v>5.448492357166543</v>
+        <v>3.420817910634935</v>
       </c>
       <c r="P21">
-        <v>1.5482478081329</v>
+        <v>1.614011677174695</v>
       </c>
       <c r="Q21">
-        <v>0.581364133429465</v>
+        <v>0.2232985729528257</v>
       </c>
       <c r="R21">
-        <v>0.5215590096336744</v>
+        <v>0.1369984143920285</v>
       </c>
       <c r="S21">
-        <v>0.002253486890922358</v>
+        <v>0.10286957079677</v>
       </c>
       <c r="T21">
-        <v>0.003403316967875255</v>
+        <v>0.04821445347274776</v>
       </c>
       <c r="U21">
-        <v>0.004583616726171178</v>
+        <v>0.6569071673660187</v>
       </c>
       <c r="V21" t="b">
         <v>1</v>
@@ -2022,64 +2022,64 @@
         <v>44</v>
       </c>
       <c r="B22" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="C22" t="s">
         <v>25</v>
       </c>
       <c r="D22">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E22">
-        <v>-0.05560389925935468</v>
+        <v>0.1714784317855029</v>
       </c>
       <c r="F22">
-        <v>1.003101382447286</v>
+        <v>1.030295692952312</v>
       </c>
       <c r="G22">
-        <v>-0.4836234584553719</v>
+        <v>0.2319679734418391</v>
       </c>
       <c r="H22">
-        <v>0.2072791326153852</v>
+        <v>0.2206338734807051</v>
       </c>
       <c r="I22">
-        <v>0.03506768618544823</v>
+        <v>0.3069992222356465</v>
       </c>
       <c r="J22">
-        <v>-0.4357755400648585</v>
+        <v>-0.3517245184237945</v>
       </c>
       <c r="K22">
-        <v>0.2072791326153852</v>
+        <v>0.2206338734807051</v>
       </c>
       <c r="L22">
-        <v>0.05409631121523648</v>
+        <v>0.1283092567097345</v>
       </c>
       <c r="M22">
-        <v>-3.571392188717089</v>
+        <v>0.5155141059387697</v>
       </c>
       <c r="N22">
-        <v>1.530684796537743</v>
+        <v>0.4903257649734611</v>
       </c>
       <c r="O22">
-        <v>-3.173763549587096</v>
+        <v>-2.604646628463996</v>
       </c>
       <c r="P22">
-        <v>1.509618817951159</v>
+        <v>1.633873229144759</v>
       </c>
       <c r="Q22">
-        <v>0.4003547856932396</v>
+        <v>0.1495378304679053</v>
       </c>
       <c r="R22">
-        <v>0.3146911836494168</v>
+        <v>0.05504203385322803</v>
       </c>
       <c r="S22">
-        <v>0.02787793517381637</v>
+        <v>0.2327528458967536</v>
       </c>
       <c r="T22">
-        <v>0.05409631121523648</v>
+        <v>0.1283092567097345</v>
       </c>
       <c r="U22">
-        <v>0.03506768618544823</v>
+        <v>0.3069992222356465</v>
       </c>
       <c r="V22" t="b">
         <v>0</v>
@@ -2093,64 +2093,64 @@
         <v>44</v>
       </c>
       <c r="B23" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C23" t="s">
         <v>25</v>
       </c>
       <c r="D23">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E23">
-        <v>0.03241508463160805</v>
+        <v>-0.2034288430430156</v>
       </c>
       <c r="F23">
-        <v>1.0010518429227</v>
+        <v>1.043169802832196</v>
       </c>
       <c r="G23">
-        <v>-0.4727836167495303</v>
+        <v>0.102262167343653</v>
       </c>
       <c r="H23">
-        <v>0.2102938169547794</v>
+        <v>0.2231184225094958</v>
       </c>
       <c r="I23">
-        <v>0.04119307215965985</v>
+        <v>0.6521996228759107</v>
       </c>
       <c r="J23">
-        <v>0.4131094419712908</v>
+        <v>-0.3411150366897054</v>
       </c>
       <c r="K23">
-        <v>0.2102938169547794</v>
+        <v>0.2231184225094958</v>
       </c>
       <c r="L23">
-        <v>0.06964776743426847</v>
+        <v>0.1436842668607495</v>
       </c>
       <c r="M23">
-        <v>-3.491343701989796</v>
+        <v>0.2272623629345191</v>
       </c>
       <c r="N23">
-        <v>1.552947199059629</v>
+        <v>0.4958473033661703</v>
       </c>
       <c r="O23">
-        <v>2.488283719640237</v>
+        <v>-4.618092446265219</v>
       </c>
       <c r="P23">
-        <v>1.26666357121401</v>
+        <v>3.020627620561325</v>
       </c>
       <c r="Q23">
-        <v>0.3815216897417447</v>
+        <v>0.1410095020931046</v>
       </c>
       <c r="R23">
-        <v>0.2931676454191369</v>
+        <v>0.04556611343678285</v>
       </c>
       <c r="S23">
-        <v>0.03461555635132625</v>
+        <v>0.2546215968657244</v>
       </c>
       <c r="T23">
-        <v>0.06964776743426847</v>
+        <v>0.1436842668607495</v>
       </c>
       <c r="U23">
-        <v>0.04119307215965985</v>
+        <v>0.6521996228759107</v>
       </c>
       <c r="V23" t="b">
         <v>0</v>
@@ -2164,64 +2164,64 @@
         <v>44</v>
       </c>
       <c r="B24" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C24" t="s">
         <v>25</v>
       </c>
       <c r="D24">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E24">
-        <v>-0.0481554436383984</v>
+        <v>-0.2201509145709022</v>
       </c>
       <c r="F24">
-        <v>1.002324336765203</v>
+        <v>1.050935065739429</v>
       </c>
       <c r="G24">
-        <v>-0.4765835152770036</v>
+        <v>0.2389273416748303</v>
       </c>
       <c r="H24">
-        <v>0.2176747837933712</v>
+        <v>0.2268862919862603</v>
       </c>
       <c r="I24">
-        <v>0.04600223822670657</v>
+        <v>0.3062403951385879</v>
       </c>
       <c r="J24">
-        <v>-0.3569871805184933</v>
+        <v>0.3055746427578379</v>
       </c>
       <c r="K24">
-        <v>0.2176747837933713</v>
+        <v>0.2268862919862603</v>
       </c>
       <c r="L24">
-        <v>0.123272257514904</v>
+        <v>0.1947524996783167</v>
       </c>
       <c r="M24">
-        <v>-3.519404640063974</v>
+        <v>0.5309802603362803</v>
       </c>
       <c r="N24">
-        <v>1.607453089647976</v>
+        <v>0.5042208293999063</v>
       </c>
       <c r="O24">
-        <v>-3.672921984080114</v>
+        <v>1.712355945297054</v>
       </c>
       <c r="P24">
-        <v>2.239583218684068</v>
+        <v>1.271408149193068</v>
       </c>
       <c r="Q24">
-        <v>0.3381859178100907</v>
+        <v>0.1183156399953231</v>
       </c>
       <c r="R24">
-        <v>0.2436410489258179</v>
+        <v>0.02035071110591458</v>
       </c>
       <c r="S24">
-        <v>0.05560988889505961</v>
+        <v>0.321972094734366</v>
       </c>
       <c r="T24">
-        <v>0.123272257514904</v>
+        <v>0.1947524996783167</v>
       </c>
       <c r="U24">
-        <v>0.04600223822670657</v>
+        <v>0.3062403951385879</v>
       </c>
       <c r="V24" t="b">
         <v>0</v>
@@ -2235,64 +2235,64 @@
         <v>44</v>
       </c>
       <c r="B25" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="C25" t="s">
         <v>25</v>
       </c>
       <c r="D25">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E25">
-        <v>-0.09506810787765753</v>
+        <v>-0.1706970786707254</v>
       </c>
       <c r="F25">
-        <v>1.009120374580511</v>
+        <v>1.030011966109139</v>
       </c>
       <c r="G25">
-        <v>-0.4900547115840658</v>
+        <v>0.1201264513693398</v>
       </c>
       <c r="H25">
-        <v>0.2223462642412364</v>
+        <v>0.2246647738828155</v>
       </c>
       <c r="I25">
-        <v>0.04476199304758969</v>
+        <v>0.5994062327275498</v>
       </c>
       <c r="J25">
-        <v>-0.3225274284159519</v>
+        <v>-0.3018701528693059</v>
       </c>
       <c r="K25">
-        <v>0.2223462642412364</v>
+        <v>0.2246647738828154</v>
       </c>
       <c r="L25">
-        <v>0.1689359777759444</v>
+        <v>0.1957569428190575</v>
       </c>
       <c r="M25">
-        <v>-3.618884771605516</v>
+        <v>0.2669630607122975</v>
       </c>
       <c r="N25">
-        <v>1.641950359144654</v>
+        <v>0.4992838378750343</v>
       </c>
       <c r="O25">
-        <v>-5.148894252685889</v>
+        <v>-2.412590868246103</v>
       </c>
       <c r="P25">
-        <v>3.549581527625693</v>
+        <v>1.795554070961514</v>
       </c>
       <c r="Q25">
-        <v>0.3141253763742617</v>
+        <v>0.1179357899494229</v>
       </c>
       <c r="R25">
-        <v>0.2161432872848706</v>
+        <v>0.01992865549935874</v>
       </c>
       <c r="S25">
-        <v>0.0714024549998958</v>
+        <v>0.3232226656169321</v>
       </c>
       <c r="T25">
-        <v>0.1689359777759444</v>
+        <v>0.1957569428190575</v>
       </c>
       <c r="U25">
-        <v>0.04476199304758969</v>
+        <v>0.5994062327275498</v>
       </c>
       <c r="V25" t="b">
         <v>0</v>
@@ -2306,64 +2306,64 @@
         <v>44</v>
       </c>
       <c r="B26" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="C26" t="s">
         <v>25</v>
       </c>
       <c r="D26">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E26">
-        <v>-0.2726521113204603</v>
+        <v>0.1715516750277424</v>
       </c>
       <c r="F26">
-        <v>1.080309300884302</v>
+        <v>1.030322363676623</v>
       </c>
       <c r="G26">
-        <v>-0.5207288680832732</v>
+        <v>0.2037789331449954</v>
       </c>
       <c r="H26">
-        <v>0.2393012779507523</v>
+        <v>0.2315285700515658</v>
       </c>
       <c r="I26">
-        <v>0.04716892439075019</v>
+        <v>0.39038028500283</v>
       </c>
       <c r="J26">
-        <v>-0.2249615033615768</v>
+        <v>-0.187256280288635</v>
       </c>
       <c r="K26">
-        <v>0.2393012779507523</v>
+        <v>0.2315285700515658</v>
       </c>
       <c r="L26">
-        <v>0.3631163930112545</v>
+        <v>0.4292013698874435</v>
       </c>
       <c r="M26">
-        <v>-3.845402821963622</v>
+        <v>0.4528681824938985</v>
       </c>
       <c r="N26">
-        <v>1.767157278832037</v>
+        <v>0.5145375976625526</v>
       </c>
       <c r="O26">
-        <v>-1.616366598795275</v>
+        <v>-2.298475889675591</v>
       </c>
       <c r="P26">
-        <v>1.719399039163273</v>
+        <v>2.841895797643314</v>
       </c>
       <c r="Q26">
-        <v>0.2578871419992098</v>
+        <v>0.06349832681584605</v>
       </c>
       <c r="R26">
-        <v>0.1518710194276682</v>
+        <v>-0.04055741464906015</v>
       </c>
       <c r="S26">
-        <v>0.1239623196254363</v>
+        <v>0.5540857980072849</v>
       </c>
       <c r="T26">
-        <v>0.3631163930112545</v>
+        <v>0.4292013698874435</v>
       </c>
       <c r="U26">
-        <v>0.04716892439075019</v>
+        <v>0.39038028500283</v>
       </c>
       <c r="V26" t="b">
         <v>0</v>
@@ -2377,64 +2377,64 @@
         <v>44</v>
       </c>
       <c r="B27" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C27" t="s">
         <v>25</v>
       </c>
       <c r="D27">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E27">
-        <v>0.293444102037538</v>
+        <v>0.3270279759063123</v>
       </c>
       <c r="F27">
-        <v>1.094222924369393</v>
+        <v>1.119754743106599</v>
       </c>
       <c r="G27">
-        <v>-0.398807958063214</v>
+        <v>0.2250334126775967</v>
       </c>
       <c r="H27">
-        <v>0.2421142500748128</v>
+        <v>0.2426839376680917</v>
       </c>
       <c r="I27">
-        <v>0.1217724614288306</v>
+        <v>0.3660540840994796</v>
       </c>
       <c r="J27">
-        <v>-0.2064607219638391</v>
+        <v>-0.1632233692779639</v>
       </c>
       <c r="K27">
-        <v>0.2421142500748128</v>
+        <v>0.2426839376680917</v>
       </c>
       <c r="L27">
-        <v>0.4081553476384943</v>
+        <v>0.5097598228639978</v>
       </c>
       <c r="M27">
-        <v>-2.945059015073826</v>
+        <v>0.5001030824280053</v>
       </c>
       <c r="N27">
-        <v>1.7879301063186</v>
+        <v>0.5393287327400571</v>
       </c>
       <c r="O27">
-        <v>-3.050984114557065</v>
+        <v>-0.7131593565170846</v>
       </c>
       <c r="P27">
-        <v>3.577855990523608</v>
+        <v>1.060340327429906</v>
       </c>
       <c r="Q27">
-        <v>0.2499971230971949</v>
+        <v>0.05325796442132023</v>
       </c>
       <c r="R27">
-        <v>0.1428538549682228</v>
+        <v>-0.05193559508742207</v>
       </c>
       <c r="S27">
-        <v>0.1334874709482317</v>
+        <v>0.6110615297376543</v>
       </c>
       <c r="T27">
-        <v>0.4081553476384943</v>
+        <v>0.5097598228639978</v>
       </c>
       <c r="U27">
-        <v>0.1217724614288306</v>
+        <v>0.3660540840994796</v>
       </c>
       <c r="V27" t="b">
         <v>0</v>
@@ -2448,64 +2448,64 @@
         <v>44</v>
       </c>
       <c r="B28" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C28" t="s">
         <v>25</v>
       </c>
       <c r="D28">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E28">
-        <v>-0.4141678597831616</v>
+        <v>-0.1417189370750191</v>
       </c>
       <c r="F28">
-        <v>1.207051618844742</v>
+        <v>1.020495902093338</v>
       </c>
       <c r="G28">
-        <v>-0.5333107068896011</v>
+        <v>0.1908656151947711</v>
       </c>
       <c r="H28">
-        <v>0.2564121484615998</v>
+        <v>0.2323851282888506</v>
       </c>
       <c r="I28">
-        <v>0.0563890368503555</v>
+        <v>0.422202188286493</v>
       </c>
       <c r="J28">
-        <v>-0.1784736934980578</v>
+        <v>0.1355557061692199</v>
       </c>
       <c r="K28">
-        <v>0.2564121484615998</v>
+        <v>0.2323851282888506</v>
       </c>
       <c r="L28">
-        <v>0.497795655580913</v>
+        <v>0.5669132740463704</v>
       </c>
       <c r="M28">
-        <v>-3.938315355561831</v>
+        <v>0.4241702658848109</v>
       </c>
       <c r="N28">
-        <v>1.893515147161597</v>
+        <v>0.5164411701571802</v>
       </c>
       <c r="O28">
-        <v>-2.224073740565115</v>
+        <v>0.9759136610640332</v>
       </c>
       <c r="P28">
-        <v>3.19531419436632</v>
+        <v>1.673023052545632</v>
       </c>
       <c r="Q28">
-        <v>0.2374305755186566</v>
+        <v>0.04747166617436132</v>
       </c>
       <c r="R28">
-        <v>0.1284920863070362</v>
+        <v>-0.05836481536182081</v>
       </c>
       <c r="S28">
-        <v>0.1499531925851488</v>
+        <v>0.6455072542144316</v>
       </c>
       <c r="T28">
-        <v>0.497795655580913</v>
+        <v>0.5669132740463704</v>
       </c>
       <c r="U28">
-        <v>0.0563890368503555</v>
+        <v>0.422202188286493</v>
       </c>
       <c r="V28" t="b">
         <v>0</v>
@@ -2519,64 +2519,64 @@
         <v>44</v>
       </c>
       <c r="B29" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C29" t="s">
         <v>25</v>
       </c>
       <c r="D29">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E29">
-        <v>-0.0169703027862131</v>
+        <v>-0.2645061627634546</v>
       </c>
       <c r="F29">
-        <v>1.000288074139466</v>
+        <v>1.075226629172762</v>
       </c>
       <c r="G29">
-        <v>-0.4568664549955076</v>
+        <v>0.2031990905148556</v>
       </c>
       <c r="H29">
-        <v>0.2340675491382252</v>
+        <v>0.2391329682913458</v>
       </c>
       <c r="I29">
-        <v>0.07125278390412024</v>
+        <v>0.4066343694924822</v>
       </c>
       <c r="J29">
-        <v>0.1488591136075246</v>
+        <v>0.1192572815063283</v>
       </c>
       <c r="K29">
-        <v>0.2340675491382252</v>
+        <v>0.2391329682913458</v>
       </c>
       <c r="L29">
-        <v>0.5350572518374678</v>
+        <v>0.6240252540660823</v>
       </c>
       <c r="M29">
-        <v>-3.373800960501566</v>
+        <v>0.4515795690244334</v>
       </c>
       <c r="N29">
-        <v>1.728507999372721</v>
+        <v>0.531437234718551</v>
       </c>
       <c r="O29">
-        <v>1.183393424319971</v>
+        <v>0.8320748011904057</v>
       </c>
       <c r="P29">
-        <v>1.860779577306753</v>
+        <v>1.668464302857133</v>
       </c>
       <c r="Q29">
-        <v>0.2331942510722033</v>
+        <v>0.04269262916148483</v>
       </c>
       <c r="R29">
-        <v>0.1236505726539466</v>
+        <v>-0.06367485648723914</v>
       </c>
       <c r="S29">
-        <v>0.1558825571892798</v>
+        <v>0.6752469406393825</v>
       </c>
       <c r="T29">
-        <v>0.5350572518374678</v>
+        <v>0.6240252540660823</v>
       </c>
       <c r="U29">
-        <v>0.07125278390412024</v>
+        <v>0.4066343694924822</v>
       </c>
       <c r="V29" t="b">
         <v>0</v>
@@ -2590,64 +2590,64 @@
         <v>44</v>
       </c>
       <c r="B30" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="C30" t="s">
         <v>25</v>
       </c>
       <c r="D30">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E30">
-        <v>-0.05461492028245667</v>
+        <v>0.1861431516411379</v>
       </c>
       <c r="F30">
-        <v>1.002991713168136</v>
+        <v>1.03589293707489</v>
       </c>
       <c r="G30">
-        <v>-0.4669066529081395</v>
+        <v>0.1545811649279696</v>
       </c>
       <c r="H30">
-        <v>0.2348844724490876</v>
+        <v>0.2353433457195432</v>
       </c>
       <c r="I30">
-        <v>0.06675309637726333</v>
+        <v>0.5195989636249763</v>
       </c>
       <c r="J30">
-        <v>-0.1375817019115678</v>
+        <v>0.09172316855879835</v>
       </c>
       <c r="K30">
-        <v>0.2348844724490877</v>
+        <v>0.2353433457195432</v>
       </c>
       <c r="L30">
-        <v>0.5673721116593613</v>
+        <v>0.7013004356267192</v>
       </c>
       <c r="M30">
-        <v>-3.447944354026917</v>
+        <v>0.3435335052957038</v>
       </c>
       <c r="N30">
-        <v>1.734540695843883</v>
+        <v>0.5230153656865397</v>
       </c>
       <c r="O30">
-        <v>-0.9228394500576481</v>
+        <v>0.5096642556860471</v>
       </c>
       <c r="P30">
-        <v>1.57550498627588</v>
+        <v>1.307696768564257</v>
       </c>
       <c r="Q30">
-        <v>0.2299138612742182</v>
+        <v>0.03758700242170271</v>
       </c>
       <c r="R30">
-        <v>0.1199015557419637</v>
+        <v>-0.06934777508699708</v>
       </c>
       <c r="S30">
-        <v>0.1606109475205406</v>
+        <v>0.7083588373351387</v>
       </c>
       <c r="T30">
-        <v>0.5673721116593613</v>
+        <v>0.7013004356267192</v>
       </c>
       <c r="U30">
-        <v>0.06675309637726333</v>
+        <v>0.5195989636249763</v>
       </c>
       <c r="V30" t="b">
         <v>0</v>
@@ -2661,64 +2661,64 @@
         <v>44</v>
       </c>
       <c r="B31" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C31" t="s">
         <v>25</v>
       </c>
       <c r="D31">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E31">
-        <v>0.2197493690321129</v>
+        <v>-0.1772276478228739</v>
       </c>
       <c r="F31">
-        <v>1.05074000934166</v>
+        <v>1.032428197122834</v>
       </c>
       <c r="G31">
-        <v>-0.4881622468581487</v>
+        <v>0.1591283378157438</v>
       </c>
       <c r="H31">
-        <v>0.2408096594600458</v>
+        <v>0.2353498153599484</v>
       </c>
       <c r="I31">
-        <v>0.06212650874073982</v>
+        <v>0.5075499999766055</v>
       </c>
       <c r="J31">
-        <v>0.1309200920983301</v>
+        <v>-0.07068009388010985</v>
       </c>
       <c r="K31">
-        <v>0.2408096594600458</v>
+        <v>0.2353498153599483</v>
       </c>
       <c r="L31">
-        <v>0.5952231920428072</v>
+        <v>0.7673745014611114</v>
       </c>
       <c r="M31">
-        <v>-3.604909573294935</v>
+        <v>0.3536389165341982</v>
       </c>
       <c r="N31">
-        <v>1.778296155256894</v>
+        <v>0.5230297434941301</v>
       </c>
       <c r="O31">
-        <v>0.8259256404008195</v>
+        <v>-0.4631851313621342</v>
       </c>
       <c r="P31">
-        <v>1.519177606863132</v>
+        <v>1.542308861791537</v>
       </c>
       <c r="Q31">
-        <v>0.2273539771666739</v>
+        <v>0.03430413524370973</v>
       </c>
       <c r="R31">
-        <v>0.1169759739047702</v>
+        <v>-0.072995405284767</v>
       </c>
       <c r="S31">
-        <v>0.164385691920056</v>
+        <v>0.7304043403794804</v>
       </c>
       <c r="T31">
-        <v>0.5952231920428072</v>
+        <v>0.7673745014611114</v>
       </c>
       <c r="U31">
-        <v>0.06212650874073982</v>
+        <v>0.5075499999766055</v>
       </c>
       <c r="V31" t="b">
         <v>0</v>
@@ -2732,64 +2732,64 @@
         <v>44</v>
       </c>
       <c r="B32" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C32" t="s">
         <v>25</v>
       </c>
       <c r="D32">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E32">
-        <v>0.1318121803859448</v>
+        <v>-0.08170346630645381</v>
       </c>
       <c r="F32">
-        <v>1.017681660032122</v>
+        <v>1.006720317593624</v>
       </c>
       <c r="G32">
-        <v>-0.4754847166404753</v>
+        <v>0.1662542325671689</v>
       </c>
       <c r="H32">
-        <v>0.2372467287043575</v>
+        <v>0.232461199011164</v>
       </c>
       <c r="I32">
-        <v>0.06479240799018404</v>
+        <v>0.4836650411531993</v>
       </c>
       <c r="J32">
-        <v>0.1220833868876404</v>
+        <v>-0.06609966845947787</v>
       </c>
       <c r="K32">
-        <v>0.2372467287043575</v>
+        <v>0.232461199011164</v>
       </c>
       <c r="L32">
-        <v>0.6148709436016768</v>
+        <v>0.7793896764108833</v>
       </c>
       <c r="M32">
-        <v>-3.511290391677422</v>
+        <v>0.3694751511974964</v>
       </c>
       <c r="N32">
-        <v>1.751985142324548</v>
+        <v>0.5166102259532007</v>
       </c>
       <c r="O32">
-        <v>0.6805961087246314</v>
+        <v>-0.4882420966250196</v>
       </c>
       <c r="P32">
-        <v>1.322614030297522</v>
+        <v>1.717063728674455</v>
       </c>
       <c r="Q32">
-        <v>0.2256869953733924</v>
+        <v>0.03380537193510548</v>
       </c>
       <c r="R32">
-        <v>0.1150708518553056</v>
+        <v>-0.07354958673877166</v>
       </c>
       <c r="S32">
-        <v>0.1668844505736522</v>
+        <v>0.7338065208990305</v>
       </c>
       <c r="T32">
-        <v>0.6148709436016768</v>
+        <v>0.7793896764108833</v>
       </c>
       <c r="U32">
-        <v>0.06479240799018404</v>
+        <v>0.4836650411531993</v>
       </c>
       <c r="V32" t="b">
         <v>0</v>
@@ -2803,64 +2803,64 @@
         <v>44</v>
       </c>
       <c r="B33" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C33" t="s">
         <v>25</v>
       </c>
       <c r="D33">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E33">
-        <v>-0.1267330293442815</v>
+        <v>0.1567930952444511</v>
       </c>
       <c r="F33">
-        <v>1.016323435683244</v>
+        <v>1.025203683966085</v>
       </c>
       <c r="G33">
-        <v>-0.4706440070748561</v>
+        <v>0.1621310857716531</v>
       </c>
       <c r="H33">
-        <v>0.2381408666342388</v>
+        <v>0.2346754551146953</v>
       </c>
       <c r="I33">
-        <v>0.06816174184725048</v>
+        <v>0.4984584258064347</v>
       </c>
       <c r="J33">
-        <v>-0.08878007499036576</v>
+        <v>0.0607406774865592</v>
       </c>
       <c r="K33">
-        <v>0.2381408666342387</v>
+        <v>0.2346754551146953</v>
       </c>
       <c r="L33">
-        <v>0.7148771940079472</v>
+        <v>0.7987042960739635</v>
       </c>
       <c r="M33">
-        <v>-3.475543423600818</v>
+        <v>0.3603120744916615</v>
       </c>
       <c r="N33">
-        <v>1.758588042085888</v>
+        <v>0.5215310787700558</v>
       </c>
       <c r="O33">
-        <v>-0.5598100758505952</v>
+        <v>0.6059630759162202</v>
       </c>
       <c r="P33">
-        <v>1.501616850719117</v>
+        <v>2.3411767288043</v>
       </c>
       <c r="Q33">
-        <v>0.218796905411774</v>
+        <v>0.03306410062412257</v>
       </c>
       <c r="R33">
-        <v>0.1071964633277418</v>
+        <v>-0.0743732215287527</v>
       </c>
       <c r="S33">
-        <v>0.1775610419942558</v>
+        <v>0.7388889317016045</v>
       </c>
       <c r="T33">
-        <v>0.7148771940079472</v>
+        <v>0.7987042960739635</v>
       </c>
       <c r="U33">
-        <v>0.06816174184725048</v>
+        <v>0.4984584258064347</v>
       </c>
       <c r="V33" t="b">
         <v>0</v>
@@ -2874,64 +2874,64 @@
         <v>44</v>
       </c>
       <c r="B34" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="C34" t="s">
         <v>25</v>
       </c>
       <c r="D34">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E34">
-        <v>-0.2384055215957291</v>
+        <v>0.08929596123652878</v>
       </c>
       <c r="F34">
-        <v>1.060262334656396</v>
+        <v>1.008037860735448</v>
       </c>
       <c r="G34">
-        <v>-0.4755477581976949</v>
+        <v>0.1770294234989691</v>
       </c>
       <c r="H34">
-        <v>0.2437667251756668</v>
+        <v>0.2327030720919852</v>
       </c>
       <c r="I34">
-        <v>0.07138513624976332</v>
+        <v>0.4566557671637366</v>
       </c>
       <c r="J34">
-        <v>-0.06776319132060642</v>
+        <v>-0.06018882402438239</v>
       </c>
       <c r="K34">
-        <v>0.2437667251756668</v>
+        <v>0.2327030720919852</v>
       </c>
       <c r="L34">
-        <v>0.785088009960876</v>
+        <v>0.7988392583699914</v>
       </c>
       <c r="M34">
-        <v>-3.511755931801835</v>
+        <v>0.3934214004883247</v>
       </c>
       <c r="N34">
-        <v>1.800133064144692</v>
+        <v>0.517147752677947</v>
       </c>
       <c r="O34">
-        <v>-0.3182534705820456</v>
+        <v>-0.4163822163107307</v>
       </c>
       <c r="P34">
-        <v>1.144863528232096</v>
+        <v>1.609824123839423</v>
       </c>
       <c r="Q34">
-        <v>0.2153724592039121</v>
+        <v>0.03305917995210672</v>
       </c>
       <c r="R34">
-        <v>0.1032828105187568</v>
+        <v>-0.07437868894210364</v>
       </c>
       <c r="S34">
-        <v>0.1830816576793275</v>
+        <v>0.7389227737969495</v>
       </c>
       <c r="T34">
-        <v>0.785088009960876</v>
+        <v>0.7988392583699914</v>
       </c>
       <c r="U34">
-        <v>0.07138513624976332</v>
+        <v>0.4566557671637366</v>
       </c>
       <c r="V34" t="b">
         <v>0</v>
@@ -2945,64 +2945,64 @@
         <v>44</v>
       </c>
       <c r="B35" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C35" t="s">
         <v>25</v>
       </c>
       <c r="D35">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E35">
-        <v>0.05964469607587693</v>
+        <v>0.1038271129495442</v>
       </c>
       <c r="F35">
-        <v>1.003570190686829</v>
+        <v>1.010897545681999</v>
       </c>
       <c r="G35">
-        <v>-0.4630459039469703</v>
+        <v>0.1657213115300176</v>
       </c>
       <c r="H35">
-        <v>0.2372496450150543</v>
+        <v>0.2330766683912467</v>
       </c>
       <c r="I35">
-        <v>0.07126992481601897</v>
+        <v>0.4861863609096367</v>
       </c>
       <c r="J35">
-        <v>0.06125045412936962</v>
+        <v>0.05714781913353865</v>
       </c>
       <c r="K35">
-        <v>0.2372496450150543</v>
+        <v>0.2330766683912467</v>
       </c>
       <c r="L35">
-        <v>0.8000331750239781</v>
+        <v>0.8090837604811484</v>
       </c>
       <c r="M35">
-        <v>-3.419434056518695</v>
+        <v>0.3682908139464237</v>
       </c>
       <c r="N35">
-        <v>1.752006678271699</v>
+        <v>0.5179780145427131</v>
       </c>
       <c r="O35">
-        <v>0.7569837570789744</v>
+        <v>0.7312488181254284</v>
       </c>
       <c r="P35">
-        <v>2.93212728300463</v>
+        <v>2.982389194860574</v>
       </c>
       <c r="Q35">
-        <v>0.2147798687628832</v>
+        <v>0.03269603883464035</v>
       </c>
       <c r="R35">
-        <v>0.102605564300438</v>
+        <v>-0.07478217907262197</v>
       </c>
       <c r="S35">
-        <v>0.1840517612361708</v>
+        <v>0.7414240956809325</v>
       </c>
       <c r="T35">
-        <v>0.8000331750239781</v>
+        <v>0.8090837604811484</v>
       </c>
       <c r="U35">
-        <v>0.07126992481601897</v>
+        <v>0.4861863609096367</v>
       </c>
       <c r="V35" t="b">
         <v>0</v>
@@ -3016,64 +3016,64 @@
         <v>44</v>
       </c>
       <c r="B36" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C36" t="s">
         <v>25</v>
       </c>
       <c r="D36">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E36">
-        <v>0.07855954182201404</v>
+        <v>-0.1202924840099329</v>
       </c>
       <c r="F36">
-        <v>1.006209926805564</v>
+        <v>1.014682745168128</v>
       </c>
       <c r="G36">
-        <v>-0.4632572875917175</v>
+        <v>0.1783464862713508</v>
       </c>
       <c r="H36">
-        <v>0.2377630482398175</v>
+        <v>0.2335344631697276</v>
       </c>
       <c r="I36">
-        <v>0.07169979159724997</v>
+        <v>0.4549499903817087</v>
       </c>
       <c r="J36">
-        <v>0.04919387608648147</v>
+        <v>0.05562842703275355</v>
       </c>
       <c r="K36">
-        <v>0.2377630482398175</v>
+        <v>0.2335344631697275</v>
       </c>
       <c r="L36">
-        <v>0.8390647212927266</v>
+        <v>0.8144148411485996</v>
       </c>
       <c r="M36">
-        <v>-3.420995051719557</v>
+        <v>0.3963483753956596</v>
       </c>
       <c r="N36">
-        <v>1.755797983748149</v>
+        <v>0.5189953949268685</v>
       </c>
       <c r="O36">
-        <v>0.4951742452870964</v>
+        <v>0.274794173282027</v>
       </c>
       <c r="P36">
-        <v>2.393268173508791</v>
+        <v>1.153617191113501</v>
       </c>
       <c r="Q36">
-        <v>0.2134466989123721</v>
+        <v>0.03251511523353082</v>
       </c>
       <c r="R36">
-        <v>0.1010819416141395</v>
+        <v>-0.07498320529607705</v>
       </c>
       <c r="S36">
-        <v>0.1862503538953123</v>
+        <v>0.7426731070831172</v>
       </c>
       <c r="T36">
-        <v>0.8390647212927266</v>
+        <v>0.8144148411485996</v>
       </c>
       <c r="U36">
-        <v>0.07169979159724997</v>
+        <v>0.4549499903817087</v>
       </c>
       <c r="V36" t="b">
         <v>0</v>
@@ -3087,64 +3087,64 @@
         <v>44</v>
       </c>
       <c r="B37" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="C37" t="s">
         <v>25</v>
       </c>
       <c r="D37">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E37">
-        <v>0.3522932556069947</v>
+        <v>-0.4096335961289829</v>
       </c>
       <c r="F37">
-        <v>1.141696576249651</v>
+        <v>1.201633764930664</v>
       </c>
       <c r="G37">
-        <v>-0.4456621052114126</v>
+        <v>0.1568761046567571</v>
       </c>
       <c r="H37">
-        <v>0.2534380845873047</v>
+        <v>0.2543974982141856</v>
       </c>
       <c r="I37">
-        <v>0.1004980282522921</v>
+        <v>0.5451819406815378</v>
       </c>
       <c r="J37">
-        <v>-0.0389747285705043</v>
+        <v>-0.03607785124295602</v>
       </c>
       <c r="K37">
-        <v>0.2534380845873047</v>
+        <v>0.2543974982141855</v>
       </c>
       <c r="L37">
-        <v>0.8799747781213381</v>
+        <v>0.8887999028088756</v>
       </c>
       <c r="M37">
-        <v>-3.291060707523818</v>
+        <v>0.3486336653950282</v>
       </c>
       <c r="N37">
-        <v>1.871552712743451</v>
+        <v>0.5653603680674801</v>
       </c>
       <c r="O37">
-        <v>-0.1664414358012501</v>
+        <v>-0.4385787025484679</v>
       </c>
       <c r="P37">
-        <v>1.082306413221632</v>
+        <v>3.092571227343742</v>
       </c>
       <c r="Q37">
-        <v>0.2123720988777724</v>
+        <v>0.03054857332119304</v>
       </c>
       <c r="R37">
-        <v>0.09985382728888281</v>
+        <v>-0.07716825186534115</v>
       </c>
       <c r="S37">
-        <v>0.1880388757873771</v>
+        <v>0.7563703341788633</v>
       </c>
       <c r="T37">
-        <v>0.8799747781213381</v>
+        <v>0.8887999028088756</v>
       </c>
       <c r="U37">
-        <v>0.1004980282522921</v>
+        <v>0.5451819406815378</v>
       </c>
       <c r="V37" t="b">
         <v>0</v>
@@ -3158,64 +3158,64 @@
         <v>44</v>
       </c>
       <c r="B38" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="C38" t="s">
         <v>25</v>
       </c>
       <c r="D38">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E38">
-        <v>-0.3387396661957605</v>
+        <v>0.084238459884925</v>
       </c>
       <c r="F38">
-        <v>1.129617460066591</v>
+        <v>1.007146832894212</v>
       </c>
       <c r="G38">
-        <v>-0.4494707120422506</v>
+        <v>0.1709659240302271</v>
       </c>
       <c r="H38">
-        <v>0.2521851985729839</v>
+        <v>0.2330240809399767</v>
       </c>
       <c r="I38">
-        <v>0.09639161779727942</v>
+        <v>0.4725905195756939</v>
       </c>
       <c r="J38">
-        <v>0.02929071547803325</v>
+        <v>0.008177744141210161</v>
       </c>
       <c r="K38">
-        <v>0.2521851985729839</v>
+        <v>0.2330240809399767</v>
       </c>
       <c r="L38">
-        <v>0.9091851545174588</v>
+        <v>0.9723910486057636</v>
       </c>
       <c r="M38">
-        <v>-3.319185953410345</v>
+        <v>0.3799461803486253</v>
       </c>
       <c r="N38">
-        <v>1.862300582296368</v>
+        <v>0.5178611468022108</v>
       </c>
       <c r="O38">
-        <v>0.2252047353459811</v>
+        <v>0.05488311732715503</v>
       </c>
       <c r="P38">
-        <v>1.938952325879338</v>
+        <v>1.563889472872222</v>
       </c>
       <c r="Q38">
-        <v>0.2118010983491284</v>
+        <v>0.02953177288575307</v>
       </c>
       <c r="R38">
-        <v>0.09920125525614676</v>
+        <v>-0.07829803012694114</v>
       </c>
       <c r="S38">
-        <v>0.1889952013385032</v>
+        <v>0.7635401718855379</v>
       </c>
       <c r="T38">
-        <v>0.9091851545174588</v>
+        <v>0.9723910486057636</v>
       </c>
       <c r="U38">
-        <v>0.09639161779727942</v>
+        <v>0.4725905195756939</v>
       </c>
       <c r="V38" t="b">
         <v>0</v>
@@ -3229,64 +3229,64 @@
         <v>44</v>
       </c>
       <c r="B39" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="C39" t="s">
         <v>25</v>
       </c>
       <c r="D39">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E39">
-        <v>0.01699113905345145</v>
+        <v>-0.09998975614734902</v>
       </c>
       <c r="F39">
-        <v>1.000288782177404</v>
+        <v>1.010098919843532</v>
       </c>
       <c r="G39">
-        <v>-0.4594215089298375</v>
+        <v>0.1715253484265067</v>
       </c>
       <c r="H39">
-        <v>0.2374241763471677</v>
+        <v>0.2333731279443599</v>
       </c>
       <c r="I39">
-        <v>0.0734526563158576</v>
+        <v>0.4718178455602751</v>
       </c>
       <c r="J39">
-        <v>0.001699103505195413</v>
+        <v>-0.001294694381673929</v>
       </c>
       <c r="K39">
-        <v>0.2374241763471677</v>
+        <v>0.2333731279443599</v>
       </c>
       <c r="L39">
-        <v>0.9943910407898504</v>
+        <v>0.9956345868754723</v>
       </c>
       <c r="M39">
-        <v>-3.392669151246411</v>
+        <v>0.3811894173490154</v>
       </c>
       <c r="N39">
-        <v>1.75329553187319</v>
+        <v>0.5186368515330205</v>
       </c>
       <c r="O39">
-        <v>0.01767977056074099</v>
+        <v>-0.01196604088424397</v>
       </c>
       <c r="P39">
-        <v>2.47048219873338</v>
+        <v>2.15692014254007</v>
       </c>
       <c r="Q39">
-        <v>0.2110444830942129</v>
+        <v>0.02946703141759671</v>
       </c>
       <c r="R39">
-        <v>0.098336552107672</v>
+        <v>-0.07836996509155925</v>
       </c>
       <c r="S39">
-        <v>0.1902688186723476</v>
+        <v>0.7639987269726598</v>
       </c>
       <c r="T39">
-        <v>0.9943910407898504</v>
+        <v>0.9956345868754723</v>
       </c>
       <c r="U39">
-        <v>0.0734526563158576</v>
+        <v>0.4718178455602751</v>
       </c>
       <c r="V39" t="b">
         <v>0</v>
@@ -3342,34 +3342,34 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B2">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C2">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D2">
-        <v>-0.5286980752799678</v>
+        <v>0.5116398734165161</v>
       </c>
       <c r="E2">
-        <v>0.02929071547803325</v>
+        <v>0.09172316855879835</v>
       </c>
       <c r="F2">
-        <v>0.008915355404983626</v>
+        <v>0.01418859194096281</v>
       </c>
       <c r="G2">
-        <v>0.9091851545174588</v>
+        <v>0.7013004356267192</v>
       </c>
       <c r="H2">
-        <v>0.008915355404983626</v>
+        <v>0.01418859194096281</v>
       </c>
       <c r="I2">
-        <v>0.9091851545174588</v>
+        <v>0.7013004356267192</v>
       </c>
       <c r="J2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" t="b">
         <v>1</v>
@@ -3377,107 +3377,107 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B3">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C3">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D3">
-        <v>-0.4288342329460387</v>
+        <v>-0.3902103637928717</v>
       </c>
       <c r="E3">
-        <v>0.001699103505195413</v>
+        <v>-0.06609966845947787</v>
       </c>
       <c r="F3">
-        <v>0.04112387770356465</v>
+        <v>0.07587274586043942</v>
       </c>
       <c r="G3">
-        <v>0.9943910407898504</v>
+        <v>0.7793896764108833</v>
       </c>
       <c r="H3">
-        <v>0.04112387770356465</v>
+        <v>0.07587274586043942</v>
       </c>
       <c r="I3">
-        <v>0.9943910407898504</v>
+        <v>0.7793896764108833</v>
       </c>
       <c r="J3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B4">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C4">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D4">
-        <v>0.5708847029135828</v>
+        <v>0.352222156734206</v>
       </c>
       <c r="E4">
-        <v>0.1220833868876404</v>
+        <v>0.3055746427578379</v>
       </c>
       <c r="F4">
-        <v>0.00401557133453159</v>
+        <v>0.1208134706567315</v>
       </c>
       <c r="G4">
-        <v>0.6148709436016768</v>
+        <v>0.1947524996783167</v>
       </c>
       <c r="H4">
-        <v>0.00401557133453159</v>
+        <v>0.1208134706567315</v>
       </c>
       <c r="I4">
-        <v>0.6148709436016768</v>
+        <v>0.1947524996783167</v>
       </c>
       <c r="J4" t="b">
         <v>0</v>
       </c>
       <c r="K4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B5">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C5">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D5">
-        <v>-0.5709586403599395</v>
+        <v>0.3477718640603116</v>
       </c>
       <c r="E5">
-        <v>-0.06776319132060642</v>
+        <v>-0.3018701528693059</v>
       </c>
       <c r="F5">
-        <v>0.004147152292338598</v>
+        <v>0.1436017312656375</v>
       </c>
       <c r="G5">
-        <v>0.785088009960876</v>
+        <v>0.1957569428190575</v>
       </c>
       <c r="H5">
-        <v>0.004147152292338598</v>
+        <v>0.1436017312656375</v>
       </c>
       <c r="I5">
-        <v>0.785088009960876</v>
+        <v>0.1957569428190575</v>
       </c>
       <c r="J5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -3485,34 +3485,34 @@
         <v>29</v>
       </c>
       <c r="B6">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C6">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D6">
-        <v>0.4230426380593251</v>
+        <v>-0.3371592273897476</v>
       </c>
       <c r="E6">
-        <v>0.4131094419712908</v>
+        <v>-0.1632233692779639</v>
       </c>
       <c r="F6">
-        <v>0.04427980316802854</v>
+        <v>0.1554211973383916</v>
       </c>
       <c r="G6">
-        <v>0.06964776743426847</v>
+        <v>0.5097598228639978</v>
       </c>
       <c r="H6">
-        <v>0.04427980316802854</v>
+        <v>0.1554211973383916</v>
       </c>
       <c r="I6">
-        <v>0.06964776743426847</v>
+        <v>0.5097598228639978</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
       </c>
       <c r="K6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -3520,28 +3520,28 @@
         <v>30</v>
       </c>
       <c r="B7">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C7">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D7">
-        <v>0.3936455575441325</v>
+        <v>-0.3095203249505835</v>
       </c>
       <c r="E7">
-        <v>-0.3569871805184933</v>
+        <v>0.1355557061692199</v>
       </c>
       <c r="F7">
-        <v>0.06486872221967133</v>
+        <v>0.1598970911204966</v>
       </c>
       <c r="G7">
-        <v>0.123272257514904</v>
+        <v>0.5669132740463704</v>
       </c>
       <c r="H7">
-        <v>0.06486872221967133</v>
+        <v>0.1598970911204966</v>
       </c>
       <c r="I7">
-        <v>0.123272257514904</v>
+        <v>0.5669132740463704</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
@@ -3555,28 +3555,28 @@
         <v>31</v>
       </c>
       <c r="B8">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C8">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D8">
-        <v>-0.3430850043101364</v>
+        <v>-0.2782674871001408</v>
       </c>
       <c r="E8">
-        <v>0.06125045412936962</v>
+        <v>0.05562842703275355</v>
       </c>
       <c r="F8">
-        <v>0.1125200626143513</v>
+        <v>0.218011724208487</v>
       </c>
       <c r="G8">
-        <v>0.8000331750239781</v>
+        <v>0.8144148411485996</v>
       </c>
       <c r="H8">
-        <v>0.1125200626143513</v>
+        <v>0.218011724208487</v>
       </c>
       <c r="I8">
-        <v>0.8000331750239781</v>
+        <v>0.8144148411485996</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
@@ -3590,31 +3590,31 @@
         <v>32</v>
       </c>
       <c r="B9">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C9">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D9">
-        <v>-0.3207049082911491</v>
+        <v>-0.2380266638187422</v>
       </c>
       <c r="E9">
-        <v>-0.2249615033615768</v>
+        <v>0.0607406774865592</v>
       </c>
       <c r="F9">
-        <v>0.1437753082918942</v>
+        <v>0.2804036261896344</v>
       </c>
       <c r="G9">
-        <v>0.3631163930112545</v>
+        <v>0.7987042960739635</v>
       </c>
       <c r="H9">
-        <v>0.1437753082918942</v>
+        <v>0.2804036261896344</v>
       </c>
       <c r="I9">
-        <v>0.3631163930112545</v>
+        <v>0.7987042960739635</v>
       </c>
       <c r="J9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="b">
         <v>0</v>
@@ -3625,31 +3625,31 @@
         <v>33</v>
       </c>
       <c r="B10">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C10">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D10">
-        <v>-0.3065865212191919</v>
+        <v>0.1983433138929727</v>
       </c>
       <c r="E10">
-        <v>-0.1784736934980578</v>
+        <v>-0.3517245184237945</v>
       </c>
       <c r="F10">
-        <v>0.1589696883263142</v>
+        <v>0.3720738204606681</v>
       </c>
       <c r="G10">
-        <v>0.497795655580913</v>
+        <v>0.1283092567097345</v>
       </c>
       <c r="H10">
-        <v>0.1589696883263142</v>
+        <v>0.3720738204606681</v>
       </c>
       <c r="I10">
-        <v>0.497795655580913</v>
+        <v>0.1283092567097345</v>
       </c>
       <c r="J10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="b">
         <v>0</v>
@@ -3660,31 +3660,31 @@
         <v>34</v>
       </c>
       <c r="B11">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C11">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D11">
-        <v>-0.2643128108259331</v>
+        <v>0.1893029112419877</v>
       </c>
       <c r="E11">
-        <v>-0.0389747285705043</v>
+        <v>-0.3411150366897054</v>
       </c>
       <c r="F11">
-        <v>0.2316309263080703</v>
+        <v>0.394859379083636</v>
       </c>
       <c r="G11">
-        <v>0.8799747781213381</v>
+        <v>0.1436842668607495</v>
       </c>
       <c r="H11">
-        <v>0.2316309263080703</v>
+        <v>0.394859379083636</v>
       </c>
       <c r="I11">
-        <v>0.8799747781213381</v>
+        <v>0.1436842668607495</v>
       </c>
       <c r="J11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="b">
         <v>0</v>
@@ -3695,34 +3695,34 @@
         <v>35</v>
       </c>
       <c r="B12">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C12">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D12">
-        <v>0.257027977442039</v>
+        <v>-0.1786772104897687</v>
       </c>
       <c r="E12">
-        <v>0.6240062304031372</v>
+        <v>0.05714781913353865</v>
       </c>
       <c r="F12">
-        <v>0.2432283212671866</v>
+        <v>0.4228199328322441</v>
       </c>
       <c r="G12">
-        <v>0.003403316967875255</v>
+        <v>0.8090837604811484</v>
       </c>
       <c r="H12">
-        <v>0.2432283212671866</v>
+        <v>0.4228199328322441</v>
       </c>
       <c r="I12">
-        <v>0.003403316967875255</v>
+        <v>0.8090837604811484</v>
       </c>
       <c r="J12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -3730,28 +3730,28 @@
         <v>36</v>
       </c>
       <c r="B13">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C13">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D13">
-        <v>0.2576392412668895</v>
+        <v>0.1273692804527506</v>
       </c>
       <c r="E13">
-        <v>-0.2064607219638391</v>
+        <v>-0.06018882402438239</v>
       </c>
       <c r="F13">
-        <v>0.2483557648908256</v>
+        <v>0.5772231580489248</v>
       </c>
       <c r="G13">
-        <v>0.4081553476384943</v>
+        <v>0.7988392583699914</v>
       </c>
       <c r="H13">
-        <v>0.2483557648908256</v>
+        <v>0.5772231580489248</v>
       </c>
       <c r="I13">
-        <v>0.4081553476384943</v>
+        <v>0.7988392583699914</v>
       </c>
       <c r="J13" t="b">
         <v>1</v>
@@ -3765,28 +3765,28 @@
         <v>37</v>
       </c>
       <c r="B14">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C14">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D14">
-        <v>0.2488247224574301</v>
+        <v>-0.1233129660525213</v>
       </c>
       <c r="E14">
-        <v>-0.08878007499036576</v>
+        <v>0.1192572815063283</v>
       </c>
       <c r="F14">
-        <v>0.2774748184455648</v>
+        <v>0.5856879393918062</v>
       </c>
       <c r="G14">
-        <v>0.7148771940079472</v>
+        <v>0.6240252540660823</v>
       </c>
       <c r="H14">
-        <v>0.2774748184455648</v>
+        <v>0.5856879393918062</v>
       </c>
       <c r="I14">
-        <v>0.7148771940079472</v>
+        <v>0.6240252540660823</v>
       </c>
       <c r="J14" t="b">
         <v>1</v>
@@ -3800,31 +3800,31 @@
         <v>38</v>
       </c>
       <c r="B15">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C15">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D15">
-        <v>0.2327545010319998</v>
+        <v>0.1281307330369182</v>
       </c>
       <c r="E15">
-        <v>-0.1375817019115678</v>
+        <v>0.008177744141210161</v>
       </c>
       <c r="F15">
-        <v>0.3001270013450621</v>
+        <v>0.6332863400645941</v>
       </c>
       <c r="G15">
-        <v>0.5673721116593613</v>
+        <v>0.9723910486057636</v>
       </c>
       <c r="H15">
-        <v>0.3001270013450621</v>
+        <v>0.6332863400645941</v>
       </c>
       <c r="I15">
-        <v>0.5673721116593613</v>
+        <v>0.9723910486057636</v>
       </c>
       <c r="J15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="b">
         <v>0</v>
@@ -3835,28 +3835,28 @@
         <v>39</v>
       </c>
       <c r="B16">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C16">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D16">
-        <v>0.1884841305723298</v>
+        <v>-0.08249336304585529</v>
       </c>
       <c r="E16">
-        <v>0.1309200920983301</v>
+        <v>-0.187256280288635</v>
       </c>
       <c r="F16">
-        <v>0.3952604688047515</v>
+        <v>0.7114809024930642</v>
       </c>
       <c r="G16">
-        <v>0.5952231920428072</v>
+        <v>0.4292013698874435</v>
       </c>
       <c r="H16">
-        <v>0.3952604688047515</v>
+        <v>0.7114809024930642</v>
       </c>
       <c r="I16">
-        <v>0.5952231920428072</v>
+        <v>0.4292013698874435</v>
       </c>
       <c r="J16" t="b">
         <v>0</v>
@@ -3870,28 +3870,28 @@
         <v>40</v>
       </c>
       <c r="B17">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C17">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D17">
-        <v>0.1575659405735668</v>
+        <v>0.08815741783247108</v>
       </c>
       <c r="E17">
-        <v>-0.4357755400648585</v>
+        <v>-0.001294694381673929</v>
       </c>
       <c r="F17">
-        <v>0.4809097599196833</v>
+        <v>0.7341200683749995</v>
       </c>
       <c r="G17">
-        <v>0.05409631121523648</v>
+        <v>0.9956345868754723</v>
       </c>
       <c r="H17">
-        <v>0.4809097599196833</v>
+        <v>0.7341200683749995</v>
       </c>
       <c r="I17">
-        <v>0.05409631121523648</v>
+        <v>0.9956345868754723</v>
       </c>
       <c r="J17" t="b">
         <v>1</v>
@@ -3905,34 +3905,34 @@
         <v>41</v>
       </c>
       <c r="B18">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C18">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D18">
-        <v>-0.1114049968622884</v>
+        <v>0.06959252103844972</v>
       </c>
       <c r="E18">
-        <v>0.1488591136075246</v>
+        <v>0.446849729174709</v>
       </c>
       <c r="F18">
-        <v>0.618470367699212</v>
+        <v>0.7552806267536643</v>
       </c>
       <c r="G18">
-        <v>0.5350572518374678</v>
+        <v>0.04821445347274776</v>
       </c>
       <c r="H18">
-        <v>0.618470367699212</v>
+        <v>0.7552806267536643</v>
       </c>
       <c r="I18">
-        <v>0.5350572518374678</v>
+        <v>0.04821445347274776</v>
       </c>
       <c r="J18" t="b">
+        <v>0</v>
+      </c>
+      <c r="K18" t="b">
         <v>1</v>
-      </c>
-      <c r="K18" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -3940,28 +3940,28 @@
         <v>42</v>
       </c>
       <c r="B19">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C19">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D19">
-        <v>0.1142550696213848</v>
+        <v>-0.08025191776949758</v>
       </c>
       <c r="E19">
-        <v>0.04919387608648147</v>
+        <v>-0.03607785124295602</v>
       </c>
       <c r="F19">
-        <v>0.6203920622497769</v>
+        <v>0.7592179371724763</v>
       </c>
       <c r="G19">
-        <v>0.8390647212927266</v>
+        <v>0.8887999028088756</v>
       </c>
       <c r="H19">
-        <v>0.6203920622497769</v>
+        <v>0.7592179371724763</v>
       </c>
       <c r="I19">
-        <v>0.8390647212927266</v>
+        <v>0.8887999028088756</v>
       </c>
       <c r="J19" t="b">
         <v>0</v>
@@ -3975,31 +3975,31 @@
         <v>43</v>
       </c>
       <c r="B20">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C20">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D20">
-        <v>-0.1015885821231817</v>
+        <v>0.05864374204260177</v>
       </c>
       <c r="E20">
-        <v>-0.3225274284159519</v>
+        <v>-0.07068009388010985</v>
       </c>
       <c r="F20">
-        <v>0.6498613252573568</v>
+        <v>0.8026578492961218</v>
       </c>
       <c r="G20">
-        <v>0.1689359777759444</v>
+        <v>0.7673745014611114</v>
       </c>
       <c r="H20">
-        <v>0.6498613252573568</v>
+        <v>0.8026578492961218</v>
       </c>
       <c r="I20">
-        <v>0.1689359777759444</v>
+        <v>0.7673745014611114</v>
       </c>
       <c r="J20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="b">
         <v>0</v>
@@ -4012,7 +4012,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W7"/>
+  <dimension ref="A1:W3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:23" s="1" customFormat="1">
@@ -4097,58 +4097,58 @@
         <v>25</v>
       </c>
       <c r="D2">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E2">
-        <v>0.1072622495056885</v>
+        <v>0.1167132846248926</v>
       </c>
       <c r="F2">
-        <v>1.01163910023057</v>
+        <v>1.01381011202702</v>
       </c>
       <c r="G2">
-        <v>0.4080145151788713</v>
+        <v>0.1024484219665803</v>
       </c>
       <c r="H2">
-        <v>0.1701051819568234</v>
+        <v>0.1904435029613048</v>
       </c>
       <c r="I2">
-        <v>0.02899989459508442</v>
+        <v>0.5965501416413891</v>
       </c>
       <c r="J2">
-        <v>0.5708847029135828</v>
+        <v>0.5116398734165161</v>
       </c>
       <c r="K2">
-        <v>0.1701051819568235</v>
+        <v>0.1904435029613049</v>
       </c>
       <c r="L2">
-        <v>0.00401557133453159</v>
+        <v>0.01418859194096281</v>
       </c>
       <c r="M2">
-        <v>1.375844308585351</v>
+        <v>0.1397675755035537</v>
       </c>
       <c r="N2">
-        <v>0.5736027463473203</v>
+        <v>0.2598168538700222</v>
       </c>
       <c r="O2">
-        <v>2.58713861483516</v>
+        <v>2.397938528513136</v>
       </c>
       <c r="P2">
-        <v>0.7708836522997121</v>
+        <v>0.8925649406612035</v>
       </c>
       <c r="Q2">
-        <v>0.5423542182666672</v>
+        <v>0.2845064891361843</v>
       </c>
       <c r="R2">
-        <v>0.4851484955500006</v>
+        <v>0.2129571380498027</v>
       </c>
       <c r="S2">
-        <v>0.001924135753232891</v>
+        <v>0.03516065792606451</v>
       </c>
       <c r="T2">
-        <v>0.00401557133453159</v>
+        <v>0.01418859194096281</v>
       </c>
       <c r="U2">
-        <v>0.02899989459508442</v>
+        <v>0.5965501416413891</v>
       </c>
       <c r="V2" t="b">
         <v>1</v>
@@ -4159,356 +4159,72 @@
     </row>
     <row r="3" spans="1:23">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="C3" t="s">
         <v>25</v>
       </c>
       <c r="D3">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E3">
-        <v>0.130591593814251</v>
+        <v>0.1710408821198426</v>
       </c>
       <c r="F3">
-        <v>1.017350055065956</v>
+        <v>1.030136629964357</v>
       </c>
       <c r="G3">
-        <v>0.5438112914683911</v>
+        <v>0.09522523274896059</v>
       </c>
       <c r="H3">
-        <v>0.1709059272915808</v>
+        <v>0.2108328182532421</v>
       </c>
       <c r="I3">
-        <v>0.005793488543173329</v>
+        <v>0.6569071673660187</v>
       </c>
       <c r="J3">
-        <v>-0.5709586403599395</v>
+        <v>0.446849729174709</v>
       </c>
       <c r="K3">
-        <v>0.1709059272915808</v>
+        <v>0.2108328182532422</v>
       </c>
       <c r="L3">
-        <v>0.004147152292338598</v>
+        <v>0.04821445347274776</v>
       </c>
       <c r="M3">
-        <v>1.833757482826876</v>
+        <v>0.2116238289062774</v>
       </c>
       <c r="N3">
-        <v>0.5763028976175987</v>
+        <v>0.4685443865017951</v>
       </c>
       <c r="O3">
-        <v>-2.630938139792167</v>
+        <v>3.420817910634935</v>
       </c>
       <c r="P3">
-        <v>0.7875227567175551</v>
+        <v>1.614011677174695</v>
       </c>
       <c r="Q3">
-        <v>0.540628740906665</v>
+        <v>0.2232985729528257</v>
       </c>
       <c r="R3">
-        <v>0.4832073335199981</v>
+        <v>0.1369984143920285</v>
       </c>
       <c r="S3">
-        <v>0.001982944495211959</v>
+        <v>0.10286957079677</v>
       </c>
       <c r="T3">
-        <v>0.004147152292338598</v>
+        <v>0.04821445347274776</v>
       </c>
       <c r="U3">
-        <v>0.005793488543173329</v>
+        <v>0.6569071673660187</v>
       </c>
       <c r="V3" t="b">
         <v>1</v>
       </c>
       <c r="W3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:23">
-      <c r="A4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4">
-        <v>19</v>
-      </c>
-      <c r="E4">
-        <v>0.07744323765729549</v>
-      </c>
-      <c r="F4">
-        <v>1.006033641552899</v>
-      </c>
-      <c r="G4">
-        <v>0.5101929833146301</v>
-      </c>
-      <c r="H4">
-        <v>0.1776564255621539</v>
-      </c>
-      <c r="I4">
-        <v>0.01106990333221139</v>
-      </c>
-      <c r="J4">
-        <v>-0.5286980752799678</v>
-      </c>
-      <c r="K4">
-        <v>0.1776564255621539</v>
-      </c>
-      <c r="L4">
-        <v>0.008915355404983626</v>
-      </c>
-      <c r="M4">
-        <v>1.720394952287141</v>
-      </c>
-      <c r="N4">
-        <v>0.5990658981486253</v>
-      </c>
-      <c r="O4">
-        <v>-3.752777077877509</v>
-      </c>
-      <c r="P4">
-        <v>1.261031565575976</v>
-      </c>
-      <c r="Q4">
-        <v>0.4980397594688339</v>
-      </c>
-      <c r="R4">
-        <v>0.4352947294024382</v>
-      </c>
-      <c r="S4">
-        <v>0.004030459392074336</v>
-      </c>
-      <c r="T4">
-        <v>0.008915355404983626</v>
-      </c>
-      <c r="U4">
-        <v>0.01106990333221139</v>
-      </c>
-      <c r="V4" t="b">
-        <v>1</v>
-      </c>
-      <c r="W4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:23">
-      <c r="A5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5">
-        <v>19</v>
-      </c>
-      <c r="E5">
-        <v>0.02564454649584646</v>
-      </c>
-      <c r="F5">
-        <v>1.000658075543598</v>
-      </c>
-      <c r="G5">
-        <v>0.4802461520475643</v>
-      </c>
-      <c r="H5">
-        <v>0.1930705584009144</v>
-      </c>
-      <c r="I5">
-        <v>0.02428101019834354</v>
-      </c>
-      <c r="J5">
-        <v>-0.4288342329460387</v>
-      </c>
-      <c r="K5">
-        <v>0.1930705584009144</v>
-      </c>
-      <c r="L5">
-        <v>0.04112387770356465</v>
-      </c>
-      <c r="M5">
-        <v>1.619412816048934</v>
-      </c>
-      <c r="N5">
-        <v>0.6510430855991501</v>
-      </c>
-      <c r="O5">
-        <v>-3.653044123033042</v>
-      </c>
-      <c r="P5">
-        <v>1.644680425468546</v>
-      </c>
-      <c r="Q5">
-        <v>0.4039723828582955</v>
-      </c>
-      <c r="R5">
-        <v>0.3294689307155825</v>
-      </c>
-      <c r="S5">
-        <v>0.01592689317284809</v>
-      </c>
-      <c r="T5">
-        <v>0.04112387770356465</v>
-      </c>
-      <c r="U5">
-        <v>0.02428101019834354</v>
-      </c>
-      <c r="V5" t="b">
-        <v>1</v>
-      </c>
-      <c r="W5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:23">
-      <c r="A6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6">
-        <v>19</v>
-      </c>
-      <c r="E6">
-        <v>-0.005597819156339884</v>
-      </c>
-      <c r="F6">
-        <v>1.000031336561257</v>
-      </c>
-      <c r="G6">
-        <v>0.471617008805046</v>
-      </c>
-      <c r="H6">
-        <v>0.1937886799420862</v>
-      </c>
-      <c r="I6">
-        <v>0.02704165709062151</v>
-      </c>
-      <c r="J6">
-        <v>0.4230426380593251</v>
-      </c>
-      <c r="K6">
-        <v>0.1937886799420862</v>
-      </c>
-      <c r="L6">
-        <v>0.04427980316802854</v>
-      </c>
-      <c r="M6">
-        <v>1.590314935516469</v>
-      </c>
-      <c r="N6">
-        <v>0.6534646255163284</v>
-      </c>
-      <c r="O6">
-        <v>2.260920041359433</v>
-      </c>
-      <c r="P6">
-        <v>1.035689244657672</v>
-      </c>
-      <c r="Q6">
-        <v>0.3991539888686922</v>
-      </c>
-      <c r="R6">
-        <v>0.3240482374772786</v>
-      </c>
-      <c r="S6">
-        <v>0.01698656083215125</v>
-      </c>
-      <c r="T6">
-        <v>0.04427980316802854</v>
-      </c>
-      <c r="U6">
-        <v>0.02704165709062151</v>
-      </c>
-      <c r="V6" t="b">
-        <v>1</v>
-      </c>
-      <c r="W6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:23">
-      <c r="A7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7">
-        <v>17</v>
-      </c>
-      <c r="E7">
-        <v>0.2212517115230526</v>
-      </c>
-      <c r="F7">
-        <v>1.051471993332927</v>
-      </c>
-      <c r="G7">
-        <v>-0.597455085703657</v>
-      </c>
-      <c r="H7">
-        <v>0.1773180937314105</v>
-      </c>
-      <c r="I7">
-        <v>0.004583616726171178</v>
-      </c>
-      <c r="J7">
-        <v>0.6240062304031372</v>
-      </c>
-      <c r="K7">
-        <v>0.1773180937314105</v>
-      </c>
-      <c r="L7">
-        <v>0.003403316967875255</v>
-      </c>
-      <c r="M7">
-        <v>-4.411999436516661</v>
-      </c>
-      <c r="N7">
-        <v>1.309432873444871</v>
-      </c>
-      <c r="O7">
-        <v>5.448492357166543</v>
-      </c>
-      <c r="P7">
-        <v>1.5482478081329</v>
-      </c>
-      <c r="Q7">
-        <v>0.581364133429465</v>
-      </c>
-      <c r="R7">
-        <v>0.5215590096336744</v>
-      </c>
-      <c r="S7">
-        <v>0.002253486890922358</v>
-      </c>
-      <c r="T7">
-        <v>0.003403316967875255</v>
-      </c>
-      <c r="U7">
-        <v>0.004583616726171178</v>
-      </c>
-      <c r="V7" t="b">
-        <v>1</v>
-      </c>
-      <c r="W7" t="b">
         <v>1</v>
       </c>
     </row>
